--- a/research/traditional_assets/database/data/ghana/ghana_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1383643468799253</v>
+        <v>0.1380521860127255</v>
       </c>
       <c r="C2">
-        <v>160.0365934825357</v>
+        <v>159.2209715735563</v>
       </c>
       <c r="D2">
-        <v>137.2365934825357</v>
+        <v>137.7009715735563</v>
       </c>
       <c r="E2">
-        <v>-87.40000000000001</v>
+        <v>-86.12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="G2">
         <v>22.8</v>
@@ -1451,28 +1451,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.064384</v>
       </c>
       <c r="N2">
-        <v>22.99133333333334</v>
+        <v>22.92694933333334</v>
       </c>
       <c r="O2">
-        <v>5.747833333333334</v>
+        <v>5.731737333333334</v>
       </c>
       <c r="P2">
-        <v>17.2435</v>
+        <v>17.195212</v>
       </c>
       <c r="Q2">
-        <v>16.5855</v>
+        <v>16.537212</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1383643468799253</v>
+        <v>0.1390655919320459</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5704007501151668</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>357.0970013253811</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1380521860127255</v>
+        <v>0.1377400251455257</v>
       </c>
       <c r="C3">
-        <v>159.2209715735563</v>
+        <v>158.4085030391244</v>
       </c>
       <c r="D3">
-        <v>137.7009715735563</v>
+        <v>138.1685030391243</v>
       </c>
       <c r="E3">
-        <v>-86.12</v>
+        <v>-84.84</v>
       </c>
       <c r="F3">
-        <v>1.28</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
         <v>22.8</v>
@@ -1533,28 +1533,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M3">
-        <v>0.064384</v>
+        <v>0.128768</v>
       </c>
       <c r="N3">
-        <v>22.92694933333334</v>
+        <v>22.86256533333334</v>
       </c>
       <c r="O3">
-        <v>5.731737333333334</v>
+        <v>5.715641333333334</v>
       </c>
       <c r="P3">
-        <v>17.195212</v>
+        <v>17.146924</v>
       </c>
       <c r="Q3">
-        <v>16.537212</v>
+        <v>16.488924</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1390655919320459</v>
+        <v>0.1397811481076793</v>
       </c>
       <c r="T3">
-        <v>0.5704007501151668</v>
+        <v>0.574777002609529</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>357.0970013253811</v>
+        <v>178.5485006626905</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1377400251455257</v>
+        <v>0.1374278642783258</v>
       </c>
       <c r="C4">
-        <v>158.4085030391244</v>
+        <v>157.5992201083052</v>
       </c>
       <c r="D4">
-        <v>138.1685030391243</v>
+        <v>138.6392201083052</v>
       </c>
       <c r="E4">
-        <v>-84.84</v>
+        <v>-83.56</v>
       </c>
       <c r="F4">
-        <v>2.56</v>
+        <v>3.84</v>
       </c>
       <c r="G4">
         <v>22.8</v>
@@ -1615,28 +1615,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M4">
-        <v>0.128768</v>
+        <v>0.193152</v>
       </c>
       <c r="N4">
-        <v>22.86256533333334</v>
+        <v>22.79818133333334</v>
       </c>
       <c r="O4">
-        <v>5.715641333333334</v>
+        <v>5.699545333333334</v>
       </c>
       <c r="P4">
-        <v>17.146924</v>
+        <v>17.098636</v>
       </c>
       <c r="Q4">
-        <v>16.488924</v>
+        <v>16.440636</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1397811481076793</v>
+        <v>0.1405114580188926</v>
       </c>
       <c r="T4">
-        <v>0.574777002609529</v>
+        <v>0.5792434871140841</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>178.5485006626905</v>
+        <v>119.032333775127</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1374278642783258</v>
+        <v>0.1371157034111261</v>
       </c>
       <c r="C5">
-        <v>157.5992201083052</v>
+        <v>156.7931554508614</v>
       </c>
       <c r="D5">
-        <v>138.6392201083052</v>
+        <v>139.1131554508614</v>
       </c>
       <c r="E5">
-        <v>-83.56</v>
+        <v>-82.28</v>
       </c>
       <c r="F5">
-        <v>3.84</v>
+        <v>5.12</v>
       </c>
       <c r="G5">
         <v>22.8</v>
@@ -1697,28 +1697,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M5">
-        <v>0.193152</v>
+        <v>0.257536</v>
       </c>
       <c r="N5">
-        <v>22.79818133333334</v>
+        <v>22.73379733333334</v>
       </c>
       <c r="O5">
-        <v>5.699545333333334</v>
+        <v>5.683449333333334</v>
       </c>
       <c r="P5">
-        <v>17.098636</v>
+        <v>17.050348</v>
       </c>
       <c r="Q5">
-        <v>16.440636</v>
+        <v>16.392348</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1405114580188926</v>
+        <v>0.141256982719923</v>
       </c>
       <c r="T5">
-        <v>0.5792434871140841</v>
+        <v>0.5838030233791509</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>119.032333775127</v>
+        <v>89.27425033134527</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1371157034111261</v>
+        <v>0.1368035425439262</v>
       </c>
       <c r="C6">
-        <v>156.7931554508614</v>
+        <v>155.9903421848117</v>
       </c>
       <c r="D6">
-        <v>139.1131554508614</v>
+        <v>139.5903421848117</v>
       </c>
       <c r="E6">
-        <v>-82.28</v>
+        <v>-81</v>
       </c>
       <c r="F6">
-        <v>5.12</v>
+        <v>6.4</v>
       </c>
       <c r="G6">
         <v>22.8</v>
@@ -1779,28 +1779,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M6">
-        <v>0.257536</v>
+        <v>0.32192</v>
       </c>
       <c r="N6">
-        <v>22.73379733333334</v>
+        <v>22.66941333333334</v>
       </c>
       <c r="O6">
-        <v>5.683449333333334</v>
+        <v>5.667353333333335</v>
       </c>
       <c r="P6">
-        <v>17.050348</v>
+        <v>17.00206</v>
       </c>
       <c r="Q6">
-        <v>16.392348</v>
+        <v>16.34406</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.141256982719923</v>
+        <v>0.1420182026778171</v>
       </c>
       <c r="T6">
-        <v>0.5838030233791509</v>
+        <v>0.588458549881377</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>89.27425033134527</v>
+        <v>71.41940026507623</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1368035425439262</v>
+        <v>0.1364913816767264</v>
       </c>
       <c r="C7">
-        <v>155.9903421848117</v>
+        <v>155.1908138841454</v>
       </c>
       <c r="D7">
-        <v>139.5903421848117</v>
+        <v>140.0708138841454</v>
       </c>
       <c r="E7">
-        <v>-81</v>
+        <v>-79.72</v>
       </c>
       <c r="F7">
-        <v>6.4</v>
+        <v>7.680000000000001</v>
       </c>
       <c r="G7">
         <v>22.8</v>
@@ -1861,28 +1861,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M7">
-        <v>0.32192</v>
+        <v>0.386304</v>
       </c>
       <c r="N7">
-        <v>22.66941333333334</v>
+        <v>22.60502933333334</v>
       </c>
       <c r="O7">
-        <v>5.667353333333335</v>
+        <v>5.651257333333334</v>
       </c>
       <c r="P7">
-        <v>17.00206</v>
+        <v>16.953772</v>
       </c>
       <c r="Q7">
-        <v>16.34406</v>
+        <v>16.295772</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1420182026778171</v>
+        <v>0.1427956188050281</v>
       </c>
       <c r="T7">
-        <v>0.588458549881377</v>
+        <v>0.5932131301389696</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>71.41940026507623</v>
+        <v>59.51616688756351</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1364913816767264</v>
+        <v>0.1361792208095266</v>
       </c>
       <c r="C8">
-        <v>155.1908138841454</v>
+        <v>154.3946045866963</v>
       </c>
       <c r="D8">
-        <v>140.0708138841454</v>
+        <v>140.5546045866963</v>
       </c>
       <c r="E8">
-        <v>-79.72</v>
+        <v>-78.44000000000001</v>
       </c>
       <c r="F8">
-        <v>7.68</v>
+        <v>8.959999999999999</v>
       </c>
       <c r="G8">
         <v>22.8</v>
@@ -1943,28 +1943,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M8">
-        <v>0.386304</v>
+        <v>0.4506879999999999</v>
       </c>
       <c r="N8">
-        <v>22.60502933333334</v>
+        <v>22.54064533333334</v>
       </c>
       <c r="O8">
-        <v>5.651257333333334</v>
+        <v>5.635161333333334</v>
       </c>
       <c r="P8">
-        <v>16.953772</v>
+        <v>16.905484</v>
       </c>
       <c r="Q8">
-        <v>16.295772</v>
+        <v>16.247484</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1427956188050281</v>
+        <v>0.1435897535586308</v>
       </c>
       <c r="T8">
-        <v>0.5932131301389696</v>
+        <v>0.5980699594343599</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>59.51616688756352</v>
+        <v>51.01385733219731</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1361792208095266</v>
+        <v>0.1358670599423268</v>
       </c>
       <c r="C9">
-        <v>154.3946045866964</v>
+        <v>153.6017488021821</v>
       </c>
       <c r="D9">
-        <v>140.5546045866964</v>
+        <v>141.0417488021821</v>
       </c>
       <c r="E9">
-        <v>-78.44</v>
+        <v>-77.16000000000001</v>
       </c>
       <c r="F9">
-        <v>8.960000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="G9">
         <v>22.8</v>
@@ -2025,28 +2025,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M9">
-        <v>0.450688</v>
+        <v>0.515072</v>
       </c>
       <c r="N9">
-        <v>22.54064533333334</v>
+        <v>22.47626133333334</v>
       </c>
       <c r="O9">
-        <v>5.635161333333334</v>
+        <v>5.619065333333334</v>
       </c>
       <c r="P9">
-        <v>16.905484</v>
+        <v>16.857196</v>
       </c>
       <c r="Q9">
-        <v>16.247484</v>
+        <v>16.199196</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1435897535586308</v>
+        <v>0.1444011521112248</v>
       </c>
       <c r="T9">
-        <v>0.5980699594343599</v>
+        <v>0.6030323719753022</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.0138573321973</v>
+        <v>44.63712516567264</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1358670599423268</v>
+        <v>0.135554899075127</v>
       </c>
       <c r="C10">
-        <v>153.6017488021821</v>
+        <v>152.8122815204086</v>
       </c>
       <c r="D10">
-        <v>141.0417488021821</v>
+        <v>141.5322815204086</v>
       </c>
       <c r="E10">
-        <v>-77.16000000000001</v>
+        <v>-75.88000000000001</v>
       </c>
       <c r="F10">
-        <v>10.24</v>
+        <v>11.52</v>
       </c>
       <c r="G10">
         <v>22.8</v>
@@ -2107,28 +2107,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M10">
-        <v>0.515072</v>
+        <v>0.579456</v>
       </c>
       <c r="N10">
-        <v>22.47626133333334</v>
+        <v>22.41187733333334</v>
       </c>
       <c r="O10">
-        <v>5.619065333333334</v>
+        <v>5.602969333333334</v>
       </c>
       <c r="P10">
-        <v>16.857196</v>
+        <v>16.808908</v>
       </c>
       <c r="Q10">
-        <v>16.199196</v>
+        <v>16.150908</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1444011521112248</v>
+        <v>0.1452303835990406</v>
       </c>
       <c r="T10">
-        <v>0.6030323719753022</v>
+        <v>0.6081038485281333</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.63712516567264</v>
+        <v>39.67744459170901</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.135554899075127</v>
+        <v>0.1352427382079272</v>
       </c>
       <c r="C11">
-        <v>152.8122815204086</v>
+        <v>152.0262382196486</v>
       </c>
       <c r="D11">
-        <v>141.5322815204086</v>
+        <v>142.0262382196486</v>
       </c>
       <c r="E11">
-        <v>-75.88000000000001</v>
+        <v>-74.60000000000001</v>
       </c>
       <c r="F11">
-        <v>11.52</v>
+        <v>12.8</v>
       </c>
       <c r="G11">
         <v>22.8</v>
@@ -2189,28 +2189,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M11">
-        <v>0.579456</v>
+        <v>0.64384</v>
       </c>
       <c r="N11">
-        <v>22.41187733333334</v>
+        <v>22.34749333333334</v>
       </c>
       <c r="O11">
-        <v>5.602969333333334</v>
+        <v>5.586873333333334</v>
       </c>
       <c r="P11">
-        <v>16.808908</v>
+        <v>16.76062</v>
       </c>
       <c r="Q11">
-        <v>16.150908</v>
+        <v>16.10262</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1452303835990406</v>
+        <v>0.1460780424532524</v>
       </c>
       <c r="T11">
-        <v>0.6081038485281333</v>
+        <v>0.6132880245599162</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.67744459170901</v>
+        <v>35.70970013253811</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1352427382079272</v>
+        <v>0.1349305773407274</v>
       </c>
       <c r="C12">
-        <v>152.0262382196486</v>
+        <v>151.2436548751954</v>
       </c>
       <c r="D12">
-        <v>142.0262382196486</v>
+        <v>142.5236548751954</v>
       </c>
       <c r="E12">
-        <v>-74.60000000000001</v>
+        <v>-73.32000000000001</v>
       </c>
       <c r="F12">
-        <v>12.8</v>
+        <v>14.08</v>
       </c>
       <c r="G12">
         <v>22.8</v>
@@ -2271,28 +2271,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M12">
-        <v>0.64384</v>
+        <v>0.708224</v>
       </c>
       <c r="N12">
-        <v>22.34749333333334</v>
+        <v>22.28310933333334</v>
       </c>
       <c r="O12">
-        <v>5.586873333333334</v>
+        <v>5.570777333333334</v>
       </c>
       <c r="P12">
-        <v>16.76062</v>
+        <v>16.712332</v>
       </c>
       <c r="Q12">
-        <v>16.10262</v>
+        <v>16.054332</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1460780424532524</v>
+        <v>0.146944749821042</v>
       </c>
       <c r="T12">
-        <v>0.6132880245599162</v>
+        <v>0.618588698929492</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.70970013253811</v>
+        <v>32.46336375685283</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1349305773407274</v>
+        <v>0.1346184164735275</v>
       </c>
       <c r="C13">
-        <v>151.2436548751954</v>
+        <v>150.4645679680964</v>
       </c>
       <c r="D13">
-        <v>142.5236548751954</v>
+        <v>143.0245679680964</v>
       </c>
       <c r="E13">
-        <v>-73.32000000000001</v>
+        <v>-72.04000000000001</v>
       </c>
       <c r="F13">
-        <v>14.08</v>
+        <v>15.36</v>
       </c>
       <c r="G13">
         <v>22.8</v>
@@ -2353,28 +2353,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M13">
-        <v>0.708224</v>
+        <v>0.772608</v>
       </c>
       <c r="N13">
-        <v>22.28310933333334</v>
+        <v>22.21872533333334</v>
       </c>
       <c r="O13">
-        <v>5.570777333333334</v>
+        <v>5.554681333333335</v>
       </c>
       <c r="P13">
-        <v>16.712332</v>
+        <v>16.664044</v>
       </c>
       <c r="Q13">
-        <v>16.054332</v>
+        <v>16.006044</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.146944749821042</v>
+        <v>0.147831155083554</v>
       </c>
       <c r="T13">
-        <v>0.618588698929492</v>
+        <v>0.6240098431711035</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.46336375685283</v>
+        <v>29.75808344378176</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1346184164735275</v>
+        <v>0.1343062556063277</v>
       </c>
       <c r="C14">
-        <v>150.4645679680964</v>
+        <v>149.6890144940729</v>
       </c>
       <c r="D14">
-        <v>143.0245679680964</v>
+        <v>143.5290144940729</v>
       </c>
       <c r="E14">
-        <v>-72.04000000000001</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="F14">
-        <v>15.36</v>
+        <v>16.64</v>
       </c>
       <c r="G14">
         <v>22.8</v>
@@ -2435,28 +2435,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M14">
-        <v>0.772608</v>
+        <v>0.836992</v>
       </c>
       <c r="N14">
-        <v>22.21872533333334</v>
+        <v>22.15434133333334</v>
       </c>
       <c r="O14">
-        <v>5.554681333333335</v>
+        <v>5.538585333333335</v>
       </c>
       <c r="P14">
-        <v>16.664044</v>
+        <v>16.615756</v>
       </c>
       <c r="Q14">
-        <v>16.006044</v>
+        <v>15.95775600000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.147831155083554</v>
+        <v>0.1487379374785376</v>
       </c>
       <c r="T14">
-        <v>0.6240098431711035</v>
+        <v>0.6295556114182693</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.75808344378176</v>
+        <v>27.4690001019524</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1343062556063277</v>
+        <v>0.1339940947391279</v>
       </c>
       <c r="C15">
-        <v>149.6890144940729</v>
+        <v>148.9170319726279</v>
       </c>
       <c r="D15">
-        <v>143.5290144940729</v>
+        <v>144.0370319726278</v>
       </c>
       <c r="E15">
-        <v>-70.76000000000001</v>
+        <v>-69.48</v>
       </c>
       <c r="F15">
-        <v>16.64</v>
+        <v>17.92</v>
       </c>
       <c r="G15">
         <v>22.8</v>
@@ -2517,28 +2517,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M15">
-        <v>0.836992</v>
+        <v>0.9013760000000001</v>
       </c>
       <c r="N15">
-        <v>22.15434133333334</v>
+        <v>22.08995733333334</v>
       </c>
       <c r="O15">
-        <v>5.538585333333335</v>
+        <v>5.522489333333334</v>
       </c>
       <c r="P15">
-        <v>16.615756</v>
+        <v>16.56746800000001</v>
       </c>
       <c r="Q15">
-        <v>15.95775600000001</v>
+        <v>15.90946800000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1487379374785376</v>
+        <v>0.1496658078361952</v>
       </c>
       <c r="T15">
-        <v>0.6295556114182693</v>
+        <v>0.6352303510200205</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.4690001019524</v>
+        <v>25.50692866609865</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1339940947391279</v>
+        <v>0.1336819338719281</v>
       </c>
       <c r="C16">
-        <v>148.9170319726279</v>
+        <v>148.1486584563485</v>
       </c>
       <c r="D16">
-        <v>144.0370319726278</v>
+        <v>144.5486584563485</v>
       </c>
       <c r="E16">
-        <v>-69.48</v>
+        <v>-68.2</v>
       </c>
       <c r="F16">
-        <v>17.92</v>
+        <v>19.2</v>
       </c>
       <c r="G16">
         <v>22.8</v>
@@ -2599,28 +2599,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M16">
-        <v>0.9013760000000001</v>
+        <v>0.9657600000000001</v>
       </c>
       <c r="N16">
-        <v>22.08995733333334</v>
+        <v>22.02557333333334</v>
       </c>
       <c r="O16">
-        <v>5.522489333333334</v>
+        <v>5.506393333333334</v>
       </c>
       <c r="P16">
-        <v>16.56746800000001</v>
+        <v>16.51918</v>
       </c>
       <c r="Q16">
-        <v>15.90946800000001</v>
+        <v>15.86118</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1496658078361952</v>
+        <v>0.1506155104375625</v>
       </c>
       <c r="T16">
-        <v>0.6352303510200205</v>
+        <v>0.6410386139065186</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.50692866609865</v>
+        <v>23.8064667550254</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1336819338719281</v>
+        <v>0.1333697730047282</v>
       </c>
       <c r="C17">
-        <v>148.1486584563485</v>
+        <v>147.383932540408</v>
       </c>
       <c r="D17">
-        <v>144.5486584563485</v>
+        <v>145.0639325404079</v>
       </c>
       <c r="E17">
-        <v>-68.2</v>
+        <v>-66.92</v>
       </c>
       <c r="F17">
-        <v>19.2</v>
+        <v>20.48</v>
       </c>
       <c r="G17">
         <v>22.8</v>
@@ -2681,28 +2681,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M17">
-        <v>0.96576</v>
+        <v>1.030144</v>
       </c>
       <c r="N17">
-        <v>22.02557333333334</v>
+        <v>21.96118933333334</v>
       </c>
       <c r="O17">
-        <v>5.506393333333334</v>
+        <v>5.490297333333334</v>
       </c>
       <c r="P17">
-        <v>16.51918</v>
+        <v>16.470892</v>
       </c>
       <c r="Q17">
-        <v>15.86118</v>
+        <v>15.812892</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1506155104375625</v>
+        <v>0.1515878250056289</v>
       </c>
       <c r="T17">
-        <v>0.6410386139065186</v>
+        <v>0.6469851687665049</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.80646675502541</v>
+        <v>22.31856258283632</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1333697730047282</v>
+        <v>0.1330576121375285</v>
       </c>
       <c r="C18">
-        <v>147.383932540408</v>
+        <v>146.6228933722704</v>
       </c>
       <c r="D18">
-        <v>145.0639325404079</v>
+        <v>145.5828933722704</v>
       </c>
       <c r="E18">
-        <v>-66.92</v>
+        <v>-65.64</v>
       </c>
       <c r="F18">
-        <v>20.48</v>
+        <v>21.76</v>
       </c>
       <c r="G18">
         <v>22.8</v>
@@ -2763,28 +2763,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M18">
-        <v>1.030144</v>
+        <v>1.094528</v>
       </c>
       <c r="N18">
-        <v>21.96118933333334</v>
+        <v>21.89680533333334</v>
       </c>
       <c r="O18">
-        <v>5.490297333333334</v>
+        <v>5.474201333333334</v>
       </c>
       <c r="P18">
-        <v>16.470892</v>
+        <v>16.422604</v>
       </c>
       <c r="Q18">
-        <v>15.812892</v>
+        <v>15.764604</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1515878250056289</v>
+        <v>0.1525835688403958</v>
       </c>
       <c r="T18">
-        <v>0.6469851687665049</v>
+        <v>0.6530750141050452</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.31856258283632</v>
+        <v>21.00570596031654</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1330576121375285</v>
+        <v>0.1327454512703286</v>
       </c>
       <c r="C19">
-        <v>146.6228933722704</v>
+        <v>145.865580661606</v>
       </c>
       <c r="D19">
-        <v>145.5828933722704</v>
+        <v>146.105580661606</v>
       </c>
       <c r="E19">
-        <v>-65.64</v>
+        <v>-64.36</v>
       </c>
       <c r="F19">
-        <v>21.76</v>
+        <v>23.04</v>
       </c>
       <c r="G19">
         <v>22.8</v>
@@ -2845,28 +2845,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M19">
-        <v>1.094528</v>
+        <v>1.158912</v>
       </c>
       <c r="N19">
-        <v>21.89680533333334</v>
+        <v>21.83242133333334</v>
       </c>
       <c r="O19">
-        <v>5.474201333333334</v>
+        <v>5.458105333333334</v>
       </c>
       <c r="P19">
-        <v>16.422604</v>
+        <v>16.374316</v>
       </c>
       <c r="Q19">
-        <v>15.764604</v>
+        <v>15.716316</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1525835688403958</v>
+        <v>0.1536035991101569</v>
       </c>
       <c r="T19">
-        <v>0.6530750141050452</v>
+        <v>0.6593133922567204</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.00570596031654</v>
+        <v>19.8387222958545</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1327454512703287</v>
+        <v>0.1324332904031289</v>
       </c>
       <c r="C20">
-        <v>145.865580661606</v>
+        <v>145.112034690419</v>
       </c>
       <c r="D20">
-        <v>146.105580661606</v>
+        <v>146.632034690419</v>
       </c>
       <c r="E20">
-        <v>-64.36000000000001</v>
+        <v>-63.08000000000001</v>
       </c>
       <c r="F20">
-        <v>23.04</v>
+        <v>24.32</v>
       </c>
       <c r="G20">
         <v>22.8</v>
@@ -2927,28 +2927,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M20">
-        <v>1.158912</v>
+        <v>1.223296</v>
       </c>
       <c r="N20">
-        <v>21.83242133333334</v>
+        <v>21.76803733333334</v>
       </c>
       <c r="O20">
-        <v>5.458105333333334</v>
+        <v>5.442009333333334</v>
       </c>
       <c r="P20">
-        <v>16.374316</v>
+        <v>16.326028</v>
       </c>
       <c r="Q20">
-        <v>15.716316</v>
+        <v>15.668028</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1536035991101569</v>
+        <v>0.1546488153125048</v>
       </c>
       <c r="T20">
-        <v>0.6593133922567204</v>
+        <v>0.6657058044368321</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.83872229585451</v>
+        <v>18.79457901712532</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1324332904031289</v>
+        <v>0.132121129535929</v>
       </c>
       <c r="C21">
-        <v>145.112034690419</v>
+        <v>144.3622963233971</v>
       </c>
       <c r="D21">
-        <v>146.632034690419</v>
+        <v>147.1622963233971</v>
       </c>
       <c r="E21">
-        <v>-63.08000000000001</v>
+        <v>-61.8</v>
       </c>
       <c r="F21">
-        <v>24.32</v>
+        <v>25.6</v>
       </c>
       <c r="G21">
         <v>22.8</v>
@@ -3009,28 +3009,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M21">
-        <v>1.223296</v>
+        <v>1.28768</v>
       </c>
       <c r="N21">
-        <v>21.76803733333334</v>
+        <v>21.70365333333334</v>
       </c>
       <c r="O21">
-        <v>5.442009333333334</v>
+        <v>5.425913333333334</v>
       </c>
       <c r="P21">
-        <v>16.326028</v>
+        <v>16.27774</v>
       </c>
       <c r="Q21">
-        <v>15.668028</v>
+        <v>15.61974</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1546488153125048</v>
+        <v>0.1557201619199113</v>
       </c>
       <c r="T21">
-        <v>0.6657058044368321</v>
+        <v>0.6722580269214465</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.79457901712532</v>
+        <v>17.85485006626906</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.132121129535929</v>
+        <v>0.1318089686687292</v>
       </c>
       <c r="C22">
-        <v>144.3622963233971</v>
+        <v>143.6164070184848</v>
       </c>
       <c r="D22">
-        <v>147.1622963233971</v>
+        <v>147.6964070184848</v>
       </c>
       <c r="E22">
-        <v>-61.8</v>
+        <v>-60.52</v>
       </c>
       <c r="F22">
-        <v>25.6</v>
+        <v>26.88</v>
       </c>
       <c r="G22">
         <v>22.8</v>
@@ -3091,28 +3091,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M22">
-        <v>1.28768</v>
+        <v>1.352064</v>
       </c>
       <c r="N22">
-        <v>21.70365333333334</v>
+        <v>21.63926933333334</v>
       </c>
       <c r="O22">
-        <v>5.425913333333334</v>
+        <v>5.409817333333335</v>
       </c>
       <c r="P22">
-        <v>16.27774</v>
+        <v>16.229452</v>
       </c>
       <c r="Q22">
-        <v>15.61974</v>
+        <v>15.571452</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1557201619199113</v>
+        <v>0.1568186312262395</v>
       </c>
       <c r="T22">
-        <v>0.6722580269214465</v>
+        <v>0.6789761284563044</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.85485006626906</v>
+        <v>17.00461911073243</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1318089686687292</v>
+        <v>0.1314968078015294</v>
       </c>
       <c r="C23">
-        <v>143.6164070184848</v>
+        <v>142.8744088376887</v>
       </c>
       <c r="D23">
-        <v>147.6964070184848</v>
+        <v>148.2344088376886</v>
       </c>
       <c r="E23">
-        <v>-60.52000000000001</v>
+        <v>-59.24000000000001</v>
       </c>
       <c r="F23">
-        <v>26.88</v>
+        <v>28.16</v>
       </c>
       <c r="G23">
         <v>22.8</v>
@@ -3173,28 +3173,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M23">
-        <v>1.352064</v>
+        <v>1.416448</v>
       </c>
       <c r="N23">
-        <v>21.63926933333334</v>
+        <v>21.57488533333334</v>
       </c>
       <c r="O23">
-        <v>5.409817333333335</v>
+        <v>5.393721333333334</v>
       </c>
       <c r="P23">
-        <v>16.229452</v>
+        <v>16.181164</v>
       </c>
       <c r="Q23">
-        <v>15.571452</v>
+        <v>15.523164</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1568186312262395</v>
+        <v>0.1579452664122172</v>
       </c>
       <c r="T23">
-        <v>0.6789761284563044</v>
+        <v>0.6858664890048766</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.00461911073243</v>
+        <v>16.23168187842641</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1314968078015294</v>
+        <v>0.1311846469343296</v>
       </c>
       <c r="C24">
-        <v>142.8744088376887</v>
+        <v>142.1363444581195</v>
       </c>
       <c r="D24">
-        <v>148.2344088376886</v>
+        <v>148.7763444581194</v>
       </c>
       <c r="E24">
-        <v>-59.24000000000001</v>
+        <v>-57.96000000000001</v>
       </c>
       <c r="F24">
-        <v>28.16</v>
+        <v>29.44</v>
       </c>
       <c r="G24">
         <v>22.8</v>
@@ -3255,28 +3255,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M24">
-        <v>1.416448</v>
+        <v>1.480832</v>
       </c>
       <c r="N24">
-        <v>21.57488533333334</v>
+        <v>21.51050133333334</v>
       </c>
       <c r="O24">
-        <v>5.393721333333334</v>
+        <v>5.377625333333334</v>
       </c>
       <c r="P24">
-        <v>16.181164</v>
+        <v>16.132876</v>
       </c>
       <c r="Q24">
-        <v>15.523164</v>
+        <v>15.474876</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1579452664122172</v>
+        <v>0.1591011648497787</v>
       </c>
       <c r="T24">
-        <v>0.6858664890048766</v>
+        <v>0.6929358199573078</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.23168187842641</v>
+        <v>15.5259565793644</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1311846469343296</v>
+        <v>0.1308724860671298</v>
       </c>
       <c r="C25">
-        <v>142.1363444581195</v>
+        <v>141.4022571832774</v>
       </c>
       <c r="D25">
-        <v>148.7763444581194</v>
+        <v>149.3222571832773</v>
       </c>
       <c r="E25">
-        <v>-57.96000000000001</v>
+        <v>-56.68000000000001</v>
       </c>
       <c r="F25">
-        <v>29.44</v>
+        <v>30.72</v>
       </c>
       <c r="G25">
         <v>22.8</v>
@@ -3337,28 +3337,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M25">
-        <v>1.480832</v>
+        <v>1.545216</v>
       </c>
       <c r="N25">
-        <v>21.51050133333334</v>
+        <v>21.44611733333334</v>
       </c>
       <c r="O25">
-        <v>5.377625333333334</v>
+        <v>5.361529333333334</v>
       </c>
       <c r="P25">
-        <v>16.132876</v>
+        <v>16.084588</v>
       </c>
       <c r="Q25">
-        <v>15.474876</v>
+        <v>15.426588</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1591011648497787</v>
+        <v>0.160287481667276</v>
       </c>
       <c r="T25">
-        <v>0.6929358199573078</v>
+        <v>0.7001911859348031</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.5259565793644</v>
+        <v>14.87904172189088</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1308724860671298</v>
+        <v>0.13056032519993</v>
       </c>
       <c r="C26">
-        <v>141.4022571832774</v>
+        <v>140.6721909545863</v>
       </c>
       <c r="D26">
-        <v>149.3222571832773</v>
+        <v>149.8721909545863</v>
       </c>
       <c r="E26">
-        <v>-56.68000000000001</v>
+        <v>-55.40000000000001</v>
       </c>
       <c r="F26">
-        <v>30.72</v>
+        <v>32</v>
       </c>
       <c r="G26">
         <v>22.8</v>
@@ -3419,28 +3419,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M26">
-        <v>1.545216</v>
+        <v>1.6096</v>
       </c>
       <c r="N26">
-        <v>21.44611733333334</v>
+        <v>21.38173333333334</v>
       </c>
       <c r="O26">
-        <v>5.361529333333334</v>
+        <v>5.345433333333334</v>
       </c>
       <c r="P26">
-        <v>16.084588</v>
+        <v>16.0363</v>
       </c>
       <c r="Q26">
-        <v>15.426588</v>
+        <v>15.3783</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.160287481667276</v>
+        <v>0.1615054335999066</v>
       </c>
       <c r="T26">
-        <v>0.7001911859348031</v>
+        <v>0.7076400283383648</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.87904172189088</v>
+        <v>14.28388005301525</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.13056032519993</v>
+        <v>0.1302481643327301</v>
       </c>
       <c r="C27">
-        <v>140.6721909545863</v>
+        <v>139.9461903631843</v>
       </c>
       <c r="D27">
-        <v>149.8721909545863</v>
+        <v>150.4261903631843</v>
       </c>
       <c r="E27">
-        <v>-55.40000000000001</v>
+        <v>-54.12</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>33.28</v>
       </c>
       <c r="G27">
         <v>22.8</v>
@@ -3501,28 +3501,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M27">
-        <v>1.6096</v>
+        <v>1.673984</v>
       </c>
       <c r="N27">
-        <v>21.38173333333334</v>
+        <v>21.31734933333334</v>
       </c>
       <c r="O27">
-        <v>5.345433333333334</v>
+        <v>5.329337333333334</v>
       </c>
       <c r="P27">
-        <v>16.0363</v>
+        <v>15.988012</v>
       </c>
       <c r="Q27">
-        <v>15.3783</v>
+        <v>15.330012</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1615054335999066</v>
+        <v>0.162756303152338</v>
       </c>
       <c r="T27">
-        <v>0.7076400283383648</v>
+        <v>0.7152901908068877</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.28388005301525</v>
+        <v>13.7345000509762</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1302481643327301</v>
+        <v>0.1299360034655303</v>
       </c>
       <c r="C28">
-        <v>139.9461903631843</v>
+        <v>139.2243006619766</v>
       </c>
       <c r="D28">
-        <v>150.4261903631843</v>
+        <v>150.9843006619766</v>
       </c>
       <c r="E28">
-        <v>-54.12</v>
+        <v>-52.84</v>
       </c>
       <c r="F28">
-        <v>33.28</v>
+        <v>34.56</v>
       </c>
       <c r="G28">
         <v>22.8</v>
@@ -3583,28 +3583,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M28">
-        <v>1.673984</v>
+        <v>1.738368</v>
       </c>
       <c r="N28">
-        <v>21.31734933333334</v>
+        <v>21.25296533333334</v>
       </c>
       <c r="O28">
-        <v>5.329337333333334</v>
+        <v>5.313241333333334</v>
       </c>
       <c r="P28">
-        <v>15.988012</v>
+        <v>15.939724</v>
       </c>
       <c r="Q28">
-        <v>15.330012</v>
+        <v>15.281724</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.162756303152338</v>
+        <v>0.1640414431034662</v>
       </c>
       <c r="T28">
-        <v>0.7152901908068877</v>
+        <v>0.7231499467676988</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.7345000509762</v>
+        <v>13.225814863903</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1299360034655303</v>
+        <v>0.1299388425983306</v>
       </c>
       <c r="C29">
-        <v>139.2243006619766</v>
+        <v>137.9392059344157</v>
       </c>
       <c r="D29">
-        <v>150.9843006619766</v>
+        <v>150.9792059344157</v>
       </c>
       <c r="E29">
-        <v>-52.84</v>
+        <v>-51.56</v>
       </c>
       <c r="F29">
-        <v>34.56</v>
+        <v>35.84</v>
       </c>
       <c r="G29">
         <v>22.8</v>
@@ -3665,45 +3665,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M29">
-        <v>1.738368</v>
+        <v>1.856512</v>
       </c>
       <c r="N29">
-        <v>21.25296533333334</v>
+        <v>21.13482133333334</v>
       </c>
       <c r="O29">
-        <v>5.313241333333334</v>
+        <v>5.283705333333335</v>
       </c>
       <c r="P29">
-        <v>15.939724</v>
+        <v>15.851116</v>
       </c>
       <c r="Q29">
-        <v>15.281724</v>
+        <v>15.19311600000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1640414431034662</v>
+        <v>0.1653622813865702</v>
       </c>
       <c r="T29">
-        <v>0.7231499467676988</v>
+        <v>0.731228029282977</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.225814863903</v>
+        <v>12.38415552031624</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1299388425983306</v>
+        <v>0.1296379317311307</v>
       </c>
       <c r="C30">
-        <v>137.9392059344157</v>
+        <v>137.2011000728895</v>
       </c>
       <c r="D30">
-        <v>150.9792059344157</v>
+        <v>151.5211000728895</v>
       </c>
       <c r="E30">
-        <v>-51.56</v>
+        <v>-50.28</v>
       </c>
       <c r="F30">
-        <v>35.84</v>
+        <v>37.12</v>
       </c>
       <c r="G30">
         <v>22.8</v>
@@ -3747,28 +3747,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M30">
-        <v>1.856512</v>
+        <v>1.922816</v>
       </c>
       <c r="N30">
-        <v>21.13482133333334</v>
+        <v>21.06851733333334</v>
       </c>
       <c r="O30">
-        <v>5.283705333333335</v>
+        <v>5.267129333333334</v>
       </c>
       <c r="P30">
-        <v>15.851116</v>
+        <v>15.801388</v>
       </c>
       <c r="Q30">
-        <v>15.19311600000001</v>
+        <v>15.143388</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1653622813865702</v>
+        <v>0.1667203263818742</v>
       </c>
       <c r="T30">
-        <v>0.731228029282977</v>
+        <v>0.7395336634184038</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.38415552031624</v>
+        <v>11.95711567478809</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1296379317311307</v>
+        <v>0.1293370208639309</v>
       </c>
       <c r="C31">
-        <v>137.2011000728895</v>
+        <v>136.4668981531953</v>
       </c>
       <c r="D31">
-        <v>151.5211000728895</v>
+        <v>152.0668981531953</v>
       </c>
       <c r="E31">
-        <v>-50.28000000000001</v>
+        <v>-49.00000000000001</v>
       </c>
       <c r="F31">
-        <v>37.12</v>
+        <v>38.4</v>
       </c>
       <c r="G31">
         <v>22.8</v>
@@ -3829,28 +3829,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M31">
-        <v>1.922816</v>
+        <v>1.98912</v>
       </c>
       <c r="N31">
-        <v>21.06851733333334</v>
+        <v>21.00221333333334</v>
       </c>
       <c r="O31">
-        <v>5.267129333333334</v>
+        <v>5.250553333333334</v>
       </c>
       <c r="P31">
-        <v>15.801388</v>
+        <v>15.75166</v>
       </c>
       <c r="Q31">
-        <v>15.143388</v>
+        <v>15.09366</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1667203263818742</v>
+        <v>0.1681171726627584</v>
       </c>
       <c r="T31">
-        <v>0.7395336634184038</v>
+        <v>0.7480766013862713</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.95711567478809</v>
+        <v>11.55854515229515</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1293370208639309</v>
+        <v>0.1290361099967311</v>
       </c>
       <c r="C32">
-        <v>136.4668981531953</v>
+        <v>135.7366425153172</v>
       </c>
       <c r="D32">
-        <v>152.0668981531953</v>
+        <v>152.6166425153172</v>
       </c>
       <c r="E32">
-        <v>-49.00000000000001</v>
+        <v>-47.72000000000001</v>
       </c>
       <c r="F32">
-        <v>38.4</v>
+        <v>39.68</v>
       </c>
       <c r="G32">
         <v>22.8</v>
@@ -3911,28 +3911,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M32">
-        <v>1.98912</v>
+        <v>2.055424</v>
       </c>
       <c r="N32">
-        <v>21.00221333333334</v>
+        <v>20.93590933333334</v>
       </c>
       <c r="O32">
-        <v>5.250553333333334</v>
+        <v>5.233977333333335</v>
       </c>
       <c r="P32">
-        <v>15.75166</v>
+        <v>15.701932</v>
       </c>
       <c r="Q32">
-        <v>15.09366</v>
+        <v>15.043932</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1681171726627584</v>
+        <v>0.1695545072416393</v>
       </c>
       <c r="T32">
-        <v>0.7480766013862713</v>
+        <v>0.7568671607445119</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.55854515229515</v>
+        <v>11.18568885705983</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1290361099967311</v>
+        <v>0.1287351991295313</v>
       </c>
       <c r="C33">
-        <v>135.7366425153172</v>
+        <v>135.0103761137219</v>
       </c>
       <c r="D33">
-        <v>152.6166425153172</v>
+        <v>153.1703761137219</v>
       </c>
       <c r="E33">
-        <v>-47.72000000000001</v>
+        <v>-46.44</v>
       </c>
       <c r="F33">
-        <v>39.68</v>
+        <v>40.96</v>
       </c>
       <c r="G33">
         <v>22.8</v>
@@ -3993,28 +3993,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M33">
-        <v>2.055424</v>
+        <v>2.121728</v>
       </c>
       <c r="N33">
-        <v>20.93590933333334</v>
+        <v>20.86960533333334</v>
       </c>
       <c r="O33">
-        <v>5.233977333333335</v>
+        <v>5.217401333333334</v>
       </c>
       <c r="P33">
-        <v>15.701932</v>
+        <v>15.652204</v>
       </c>
       <c r="Q33">
-        <v>15.043932</v>
+        <v>14.994204</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1695545072416393</v>
+        <v>0.1710341163669578</v>
       </c>
       <c r="T33">
-        <v>0.7568671607445119</v>
+        <v>0.7659162659662302</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.18568885705983</v>
+        <v>10.83613608027671</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1287351991295313</v>
+        <v>0.1284342882623314</v>
       </c>
       <c r="C34">
-        <v>135.0103761137219</v>
+        <v>134.2881425285471</v>
       </c>
       <c r="D34">
-        <v>153.1703761137219</v>
+        <v>153.7281425285471</v>
       </c>
       <c r="E34">
-        <v>-46.44</v>
+        <v>-45.16</v>
       </c>
       <c r="F34">
-        <v>40.96</v>
+        <v>42.24</v>
       </c>
       <c r="G34">
         <v>22.8</v>
@@ -4075,28 +4075,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M34">
-        <v>2.121728</v>
+        <v>2.188032</v>
       </c>
       <c r="N34">
-        <v>20.86960533333334</v>
+        <v>20.80330133333334</v>
       </c>
       <c r="O34">
-        <v>5.217401333333334</v>
+        <v>5.200825333333334</v>
       </c>
       <c r="P34">
-        <v>15.652204</v>
+        <v>15.602476</v>
       </c>
       <c r="Q34">
-        <v>14.994204</v>
+        <v>14.944476</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1710341163669578</v>
+        <v>0.1725578929288529</v>
       </c>
       <c r="T34">
-        <v>0.7659162659662302</v>
+        <v>0.7752354937318803</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.83613608027671</v>
+        <v>10.50776832026832</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1284342882623314</v>
+        <v>0.1281333773951316</v>
       </c>
       <c r="C35">
-        <v>134.2881425285471</v>
+        <v>133.5699859770343</v>
       </c>
       <c r="D35">
-        <v>153.7281425285471</v>
+        <v>154.2899859770343</v>
       </c>
       <c r="E35">
-        <v>-45.16</v>
+        <v>-43.88</v>
       </c>
       <c r="F35">
-        <v>42.24</v>
+        <v>43.52</v>
       </c>
       <c r="G35">
         <v>22.8</v>
@@ -4157,28 +4157,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M35">
-        <v>2.188032</v>
+        <v>2.254336</v>
       </c>
       <c r="N35">
-        <v>20.80330133333334</v>
+        <v>20.73699733333334</v>
       </c>
       <c r="O35">
-        <v>5.200825333333334</v>
+        <v>5.184249333333335</v>
       </c>
       <c r="P35">
-        <v>15.602476</v>
+        <v>15.552748</v>
       </c>
       <c r="Q35">
-        <v>14.944476</v>
+        <v>14.89474800000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1725578929288529</v>
+        <v>0.1741278445380783</v>
       </c>
       <c r="T35">
-        <v>0.7752354937318803</v>
+        <v>0.7848371223389137</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.50776832026832</v>
+        <v>10.19871631084867</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1281333773951316</v>
+        <v>0.1278324665279318</v>
       </c>
       <c r="C36">
-        <v>133.5699859770343</v>
+        <v>132.8559513252149</v>
       </c>
       <c r="D36">
-        <v>154.2899859770343</v>
+        <v>154.8559513252149</v>
       </c>
       <c r="E36">
-        <v>-43.88</v>
+        <v>-42.6</v>
       </c>
       <c r="F36">
-        <v>43.52</v>
+        <v>44.8</v>
       </c>
       <c r="G36">
         <v>22.8</v>
@@ -4239,28 +4239,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M36">
-        <v>2.254336</v>
+        <v>2.32064</v>
       </c>
       <c r="N36">
-        <v>20.73699733333334</v>
+        <v>20.67069333333334</v>
       </c>
       <c r="O36">
-        <v>5.184249333333335</v>
+        <v>5.167673333333334</v>
       </c>
       <c r="P36">
-        <v>15.552748</v>
+        <v>15.50302</v>
       </c>
       <c r="Q36">
-        <v>14.89474800000001</v>
+        <v>14.84502</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1741278445380783</v>
+        <v>0.1757461023506644</v>
       </c>
       <c r="T36">
-        <v>0.7848371223389137</v>
+        <v>0.7947341856723175</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.19871631084867</v>
+        <v>9.907324416252989</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1278324665279318</v>
+        <v>0.127990555660732</v>
       </c>
       <c r="C37">
-        <v>132.8559513252149</v>
+        <v>131.2780941948288</v>
       </c>
       <c r="D37">
-        <v>154.8559513252149</v>
+        <v>154.5580941948288</v>
       </c>
       <c r="E37">
-        <v>-42.6</v>
+        <v>-41.32</v>
       </c>
       <c r="F37">
-        <v>44.8</v>
+        <v>46.08000000000001</v>
       </c>
       <c r="G37">
         <v>22.8</v>
@@ -4321,45 +4321,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M37">
-        <v>2.32064</v>
+        <v>2.46528</v>
       </c>
       <c r="N37">
-        <v>20.67069333333334</v>
+        <v>20.52605333333334</v>
       </c>
       <c r="O37">
-        <v>5.167673333333334</v>
+        <v>5.131513333333334</v>
       </c>
       <c r="P37">
-        <v>15.50302</v>
+        <v>15.39454</v>
       </c>
       <c r="Q37">
-        <v>14.84502</v>
+        <v>14.73654</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1757461023506644</v>
+        <v>0.1774149307198938</v>
       </c>
       <c r="T37">
-        <v>0.7947341856723175</v>
+        <v>0.8049405322348899</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.907324416252989</v>
+        <v>9.326053565247491</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.127990555660732</v>
+        <v>0.1277023947935322</v>
       </c>
       <c r="C38">
-        <v>131.2780941948287</v>
+        <v>130.5418828663103</v>
       </c>
       <c r="D38">
-        <v>154.5580941948287</v>
+        <v>155.1018828663103</v>
       </c>
       <c r="E38">
-        <v>-41.32000000000001</v>
+        <v>-40.04000000000001</v>
       </c>
       <c r="F38">
-        <v>46.08</v>
+        <v>47.36</v>
       </c>
       <c r="G38">
         <v>22.8</v>
@@ -4403,28 +4403,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M38">
-        <v>2.46528</v>
+        <v>2.53376</v>
       </c>
       <c r="N38">
-        <v>20.52605333333334</v>
+        <v>20.45757333333334</v>
       </c>
       <c r="O38">
-        <v>5.131513333333334</v>
+        <v>5.114393333333334</v>
       </c>
       <c r="P38">
-        <v>15.39454</v>
+        <v>15.34318</v>
       </c>
       <c r="Q38">
-        <v>14.73654</v>
+        <v>14.68518</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1774149307198938</v>
+        <v>0.1791367377675114</v>
       </c>
       <c r="T38">
-        <v>0.8049405322348899</v>
+        <v>0.8154708897994489</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.326053565247491</v>
+        <v>9.073998063484046</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1277023947935322</v>
+        <v>0.1274142339263324</v>
       </c>
       <c r="C39">
-        <v>130.5418828663103</v>
+        <v>129.8095115202951</v>
       </c>
       <c r="D39">
-        <v>155.1018828663103</v>
+        <v>155.6495115202951</v>
       </c>
       <c r="E39">
-        <v>-40.04000000000001</v>
+        <v>-38.76000000000001</v>
       </c>
       <c r="F39">
-        <v>47.36</v>
+        <v>48.64</v>
       </c>
       <c r="G39">
         <v>22.8</v>
@@ -4485,28 +4485,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M39">
-        <v>2.53376</v>
+        <v>2.60224</v>
       </c>
       <c r="N39">
-        <v>20.45757333333334</v>
+        <v>20.38909333333334</v>
       </c>
       <c r="O39">
-        <v>5.114393333333334</v>
+        <v>5.097273333333334</v>
       </c>
       <c r="P39">
-        <v>15.34318</v>
+        <v>15.29182</v>
       </c>
       <c r="Q39">
-        <v>14.68518</v>
+        <v>14.63382</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1791367377675114</v>
+        <v>0.1809140869779555</v>
       </c>
       <c r="T39">
-        <v>0.8154708897994489</v>
+        <v>0.8263409363177034</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.073998063484046</v>
+        <v>8.835208640760781</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1274142339263324</v>
+        <v>0.1271260730591326</v>
       </c>
       <c r="C40">
-        <v>129.8095115202951</v>
+        <v>129.0810209751572</v>
       </c>
       <c r="D40">
-        <v>155.6495115202951</v>
+        <v>156.2010209751572</v>
       </c>
       <c r="E40">
-        <v>-38.76000000000001</v>
+        <v>-37.48</v>
       </c>
       <c r="F40">
-        <v>48.64</v>
+        <v>49.92</v>
       </c>
       <c r="G40">
         <v>22.8</v>
@@ -4567,28 +4567,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M40">
-        <v>2.60224</v>
+        <v>2.67072</v>
       </c>
       <c r="N40">
-        <v>20.38909333333334</v>
+        <v>20.32061333333334</v>
       </c>
       <c r="O40">
-        <v>5.097273333333334</v>
+        <v>5.080153333333334</v>
       </c>
       <c r="P40">
-        <v>15.29182</v>
+        <v>15.24046</v>
       </c>
       <c r="Q40">
-        <v>14.63382</v>
+        <v>14.58246</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1809140869779555</v>
+        <v>0.1827497099330042</v>
       </c>
       <c r="T40">
-        <v>0.8263409363177034</v>
+        <v>0.8375673778037694</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.835208640760781</v>
+        <v>8.608664829459222</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1271260730591326</v>
+        <v>0.1268379121919327</v>
       </c>
       <c r="C41">
-        <v>129.0810209751572</v>
+        <v>128.356452629851</v>
       </c>
       <c r="D41">
-        <v>156.2010209751572</v>
+        <v>156.7564526298511</v>
       </c>
       <c r="E41">
-        <v>-37.48</v>
+        <v>-36.2</v>
       </c>
       <c r="F41">
-        <v>49.92</v>
+        <v>51.2</v>
       </c>
       <c r="G41">
         <v>22.8</v>
@@ -4649,28 +4649,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M41">
-        <v>2.67072</v>
+        <v>2.7392</v>
       </c>
       <c r="N41">
-        <v>20.32061333333334</v>
+        <v>20.25213333333334</v>
       </c>
       <c r="O41">
-        <v>5.080153333333334</v>
+        <v>5.063033333333334</v>
       </c>
       <c r="P41">
-        <v>15.24046</v>
+        <v>15.1891</v>
       </c>
       <c r="Q41">
-        <v>14.58246</v>
+        <v>14.5311</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1827497099330042</v>
+        <v>0.1846465203198879</v>
       </c>
       <c r="T41">
-        <v>0.8375673778037694</v>
+        <v>0.8491680340060377</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.608664829459222</v>
+        <v>8.393448208722742</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1268379121919327</v>
+        <v>0.126549751324733</v>
       </c>
       <c r="C42">
-        <v>128.356452629851</v>
+        <v>127.6358484742708</v>
       </c>
       <c r="D42">
-        <v>156.7564526298511</v>
+        <v>157.3158484742708</v>
       </c>
       <c r="E42">
-        <v>-36.2</v>
+        <v>-34.92</v>
       </c>
       <c r="F42">
-        <v>51.2</v>
+        <v>52.48</v>
       </c>
       <c r="G42">
         <v>22.8</v>
@@ -4731,28 +4731,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M42">
-        <v>2.7392</v>
+        <v>2.80768</v>
       </c>
       <c r="N42">
-        <v>20.25213333333334</v>
+        <v>20.18365333333334</v>
       </c>
       <c r="O42">
-        <v>5.063033333333334</v>
+        <v>5.045913333333334</v>
       </c>
       <c r="P42">
-        <v>15.1891</v>
+        <v>15.13774</v>
       </c>
       <c r="Q42">
-        <v>14.5311</v>
+        <v>14.47974</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1846465203198879</v>
+        <v>0.1866076293639542</v>
       </c>
       <c r="T42">
-        <v>0.8491680340060377</v>
+        <v>0.8611619327914338</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.393448208722742</v>
+        <v>8.188729959729505</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.126549751324733</v>
+        <v>0.1262615904575331</v>
       </c>
       <c r="C43">
-        <v>127.6358484742708</v>
+        <v>126.9192510998322</v>
       </c>
       <c r="D43">
-        <v>157.3158484742708</v>
+        <v>157.8792510998322</v>
       </c>
       <c r="E43">
-        <v>-34.92</v>
+        <v>-33.64</v>
       </c>
       <c r="F43">
-        <v>52.48</v>
+        <v>53.76000000000001</v>
       </c>
       <c r="G43">
         <v>22.8</v>
@@ -4813,28 +4813,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M43">
-        <v>2.80768</v>
+        <v>2.87616</v>
       </c>
       <c r="N43">
-        <v>20.18365333333334</v>
+        <v>20.11517333333334</v>
       </c>
       <c r="O43">
-        <v>5.045913333333334</v>
+        <v>5.028793333333335</v>
       </c>
       <c r="P43">
-        <v>15.13774</v>
+        <v>15.08638</v>
       </c>
       <c r="Q43">
-        <v>14.47974</v>
+        <v>14.42838</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1866076293639542</v>
+        <v>0.1886363628578158</v>
       </c>
       <c r="T43">
-        <v>0.8611619327914338</v>
+        <v>0.8735694142935676</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.188729959729505</v>
+        <v>7.993760198783565</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1262615904575332</v>
+        <v>0.1259734295903334</v>
       </c>
       <c r="C44">
-        <v>126.9192510998321</v>
+        <v>126.2067037102824</v>
       </c>
       <c r="D44">
-        <v>157.8792510998321</v>
+        <v>158.4467037102823</v>
       </c>
       <c r="E44">
-        <v>-33.64000000000001</v>
+        <v>-32.36000000000001</v>
       </c>
       <c r="F44">
-        <v>53.76</v>
+        <v>55.04</v>
       </c>
       <c r="G44">
         <v>22.8</v>
@@ -4895,28 +4895,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M44">
-        <v>2.87616</v>
+        <v>2.94464</v>
       </c>
       <c r="N44">
-        <v>20.11517333333334</v>
+        <v>20.04669333333334</v>
       </c>
       <c r="O44">
-        <v>5.028793333333335</v>
+        <v>5.011673333333334</v>
       </c>
       <c r="P44">
-        <v>15.08638</v>
+        <v>15.03502</v>
       </c>
       <c r="Q44">
-        <v>14.42838</v>
+        <v>14.37702</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1886363628578158</v>
+        <v>0.1907362799830409</v>
       </c>
       <c r="T44">
-        <v>0.8735694142935676</v>
+        <v>0.8864122460238464</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.993760198783565</v>
+        <v>7.807858798811854</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1259734295903334</v>
+        <v>0.1256852687231335</v>
       </c>
       <c r="C45">
-        <v>126.2067037102824</v>
+        <v>125.4982501327442</v>
       </c>
       <c r="D45">
-        <v>158.4467037102823</v>
+        <v>159.0182501327442</v>
       </c>
       <c r="E45">
-        <v>-32.36000000000001</v>
+        <v>-31.08000000000001</v>
       </c>
       <c r="F45">
-        <v>55.04</v>
+        <v>56.32</v>
       </c>
       <c r="G45">
         <v>22.8</v>
@@ -4977,28 +4977,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M45">
-        <v>2.94464</v>
+        <v>3.01312</v>
       </c>
       <c r="N45">
-        <v>20.04669333333334</v>
+        <v>19.97821333333334</v>
       </c>
       <c r="O45">
-        <v>5.011673333333334</v>
+        <v>4.994553333333334</v>
       </c>
       <c r="P45">
-        <v>15.03502</v>
+        <v>14.98366</v>
       </c>
       <c r="Q45">
-        <v>14.37702</v>
+        <v>14.32566</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1907362799830409</v>
+        <v>0.1929111941484527</v>
       </c>
       <c r="T45">
-        <v>0.8864122460238464</v>
+        <v>0.899713750315921</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.807858798811854</v>
+        <v>7.630407462475221</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1256852687231335</v>
+        <v>0.1256671078559337</v>
       </c>
       <c r="C46">
-        <v>125.4982501327442</v>
+        <v>124.2544090647569</v>
       </c>
       <c r="D46">
-        <v>159.0182501327442</v>
+        <v>159.0544090647568</v>
       </c>
       <c r="E46">
-        <v>-31.08000000000001</v>
+        <v>-29.8</v>
       </c>
       <c r="F46">
-        <v>56.32</v>
+        <v>57.6</v>
       </c>
       <c r="G46">
         <v>22.8</v>
@@ -5059,45 +5059,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M46">
-        <v>3.01312</v>
+        <v>3.12768</v>
       </c>
       <c r="N46">
-        <v>19.97821333333334</v>
+        <v>19.86365333333334</v>
       </c>
       <c r="O46">
-        <v>4.994553333333334</v>
+        <v>4.965913333333334</v>
       </c>
       <c r="P46">
-        <v>14.98366</v>
+        <v>14.89774</v>
       </c>
       <c r="Q46">
-        <v>14.32566</v>
+        <v>14.23974</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1929111941484527</v>
+        <v>0.1951651961016976</v>
       </c>
       <c r="T46">
-        <v>0.899713750315921</v>
+        <v>0.9134989456731618</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.630407462475221</v>
+        <v>7.350922515517359</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1256671078559337</v>
+        <v>0.1253849469887339</v>
       </c>
       <c r="C47">
-        <v>124.2544090647569</v>
+        <v>123.5383213583721</v>
       </c>
       <c r="D47">
-        <v>159.0544090647568</v>
+        <v>159.6183213583721</v>
       </c>
       <c r="E47">
-        <v>-29.8</v>
+        <v>-28.52</v>
       </c>
       <c r="F47">
-        <v>57.6</v>
+        <v>58.88</v>
       </c>
       <c r="G47">
         <v>22.8</v>
@@ -5141,28 +5141,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M47">
-        <v>3.12768</v>
+        <v>3.197184</v>
       </c>
       <c r="N47">
-        <v>19.86365333333334</v>
+        <v>19.79414933333334</v>
       </c>
       <c r="O47">
-        <v>4.965913333333334</v>
+        <v>4.948537333333334</v>
       </c>
       <c r="P47">
-        <v>14.89774</v>
+        <v>14.845612</v>
       </c>
       <c r="Q47">
-        <v>14.23974</v>
+        <v>14.187612</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1951651961016976</v>
+        <v>0.1975026796087665</v>
       </c>
       <c r="T47">
-        <v>0.9134989456731618</v>
+        <v>0.9277947038214116</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.350922515517359</v>
+        <v>7.191119852136548</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1253849469887339</v>
+        <v>0.1251027861215341</v>
       </c>
       <c r="C48">
-        <v>123.5383213583721</v>
+        <v>122.8262464739719</v>
       </c>
       <c r="D48">
-        <v>159.6183213583721</v>
+        <v>160.1862464739719</v>
       </c>
       <c r="E48">
-        <v>-28.52</v>
+        <v>-27.24</v>
       </c>
       <c r="F48">
-        <v>58.88</v>
+        <v>60.16</v>
       </c>
       <c r="G48">
         <v>22.8</v>
@@ -5223,28 +5223,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M48">
-        <v>3.197184</v>
+        <v>3.266688</v>
       </c>
       <c r="N48">
-        <v>19.79414933333334</v>
+        <v>19.72464533333333</v>
       </c>
       <c r="O48">
-        <v>4.948537333333334</v>
+        <v>4.931161333333334</v>
       </c>
       <c r="P48">
-        <v>14.845612</v>
+        <v>14.793484</v>
       </c>
       <c r="Q48">
-        <v>14.187612</v>
+        <v>14.135484</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1975026796087665</v>
+        <v>0.1999283700406303</v>
       </c>
       <c r="T48">
-        <v>0.9277947038214116</v>
+        <v>0.9426299245412935</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.191119852136548</v>
+        <v>7.038117302091089</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1251027861215341</v>
+        <v>0.1248206252543343</v>
       </c>
       <c r="C49">
-        <v>122.8262464739719</v>
+        <v>122.1182273975992</v>
       </c>
       <c r="D49">
-        <v>160.1862464739719</v>
+        <v>160.7582273975991</v>
       </c>
       <c r="E49">
-        <v>-27.24</v>
+        <v>-25.96</v>
       </c>
       <c r="F49">
-        <v>60.16</v>
+        <v>61.44</v>
       </c>
       <c r="G49">
         <v>22.8</v>
@@ -5305,28 +5305,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M49">
-        <v>3.266688</v>
+        <v>3.336192</v>
       </c>
       <c r="N49">
-        <v>19.72464533333333</v>
+        <v>19.65514133333334</v>
       </c>
       <c r="O49">
-        <v>4.931161333333334</v>
+        <v>4.913785333333334</v>
       </c>
       <c r="P49">
-        <v>14.793484</v>
+        <v>14.741356</v>
       </c>
       <c r="Q49">
-        <v>14.135484</v>
+        <v>14.083356</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1999283700406303</v>
+        <v>0.2024473562583351</v>
       </c>
       <c r="T49">
-        <v>0.9426299245412935</v>
+        <v>0.9580357306734785</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.038117302091089</v>
+        <v>6.891489858297524</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1248206252543343</v>
+        <v>0.1245384643871344</v>
       </c>
       <c r="C50">
-        <v>122.1182273975992</v>
+        <v>121.4143077314623</v>
       </c>
       <c r="D50">
-        <v>160.7582273975991</v>
+        <v>161.3343077314623</v>
       </c>
       <c r="E50">
-        <v>-25.96000000000001</v>
+        <v>-24.68000000000001</v>
       </c>
       <c r="F50">
-        <v>61.44</v>
+        <v>62.72</v>
       </c>
       <c r="G50">
         <v>22.8</v>
@@ -5387,28 +5387,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M50">
-        <v>3.336192</v>
+        <v>3.405696</v>
       </c>
       <c r="N50">
-        <v>19.65514133333334</v>
+        <v>19.58563733333334</v>
       </c>
       <c r="O50">
-        <v>4.913785333333334</v>
+        <v>4.896409333333335</v>
       </c>
       <c r="P50">
-        <v>14.741356</v>
+        <v>14.689228</v>
       </c>
       <c r="Q50">
-        <v>14.083356</v>
+        <v>14.031228</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2024473562583351</v>
+        <v>0.2050651262492832</v>
       </c>
       <c r="T50">
-        <v>0.9580357306734785</v>
+        <v>0.9740456860657492</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.891489858297525</v>
+        <v>6.750847208128189</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1245384643871344</v>
+        <v>0.1242563035199346</v>
       </c>
       <c r="C51">
-        <v>121.4143077314623</v>
+        <v>120.714531705015</v>
       </c>
       <c r="D51">
-        <v>161.3343077314623</v>
+        <v>161.914531705015</v>
       </c>
       <c r="E51">
-        <v>-24.68000000000001</v>
+        <v>-23.40000000000001</v>
       </c>
       <c r="F51">
-        <v>62.72</v>
+        <v>64</v>
       </c>
       <c r="G51">
         <v>22.8</v>
@@ -5469,28 +5469,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M51">
-        <v>3.405696</v>
+        <v>3.4752</v>
       </c>
       <c r="N51">
-        <v>19.58563733333334</v>
+        <v>19.51613333333334</v>
       </c>
       <c r="O51">
-        <v>4.896409333333335</v>
+        <v>4.879033333333334</v>
       </c>
       <c r="P51">
-        <v>14.689228</v>
+        <v>14.6371</v>
       </c>
       <c r="Q51">
-        <v>14.031228</v>
+        <v>13.9791</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2050651262492832</v>
+        <v>0.2077876070398693</v>
       </c>
       <c r="T51">
-        <v>0.9740456860657492</v>
+        <v>0.9906960396737107</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.750847208128189</v>
+        <v>6.615830263965623</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1242563035199346</v>
+        <v>0.1239741426527348</v>
       </c>
       <c r="C52">
-        <v>120.714531705015</v>
+        <v>120.018944186276</v>
       </c>
       <c r="D52">
-        <v>161.914531705015</v>
+        <v>162.498944186276</v>
       </c>
       <c r="E52">
-        <v>-23.40000000000001</v>
+        <v>-22.12</v>
       </c>
       <c r="F52">
-        <v>64</v>
+        <v>65.28</v>
       </c>
       <c r="G52">
         <v>22.8</v>
@@ -5551,28 +5551,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M52">
-        <v>3.4752</v>
+        <v>3.544704</v>
       </c>
       <c r="N52">
-        <v>19.51613333333334</v>
+        <v>19.44662933333334</v>
       </c>
       <c r="O52">
-        <v>4.879033333333334</v>
+        <v>4.861657333333334</v>
       </c>
       <c r="P52">
-        <v>14.6371</v>
+        <v>14.584972</v>
       </c>
       <c r="Q52">
-        <v>13.9791</v>
+        <v>13.926972</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2077876070398693</v>
+        <v>0.2106212094953772</v>
       </c>
       <c r="T52">
-        <v>0.9906960396737107</v>
+        <v>1.008025999551385</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.615830263965623</v>
+        <v>6.486108101927083</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1239741426527348</v>
+        <v>0.123691981785535</v>
       </c>
       <c r="C53">
-        <v>120.018944186276</v>
+        <v>119.3275906933953</v>
       </c>
       <c r="D53">
-        <v>162.498944186276</v>
+        <v>163.0875906933953</v>
       </c>
       <c r="E53">
-        <v>-22.12</v>
+        <v>-20.84</v>
       </c>
       <c r="F53">
-        <v>65.28</v>
+        <v>66.56</v>
       </c>
       <c r="G53">
         <v>22.8</v>
@@ -5633,28 +5633,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M53">
-        <v>3.544704</v>
+        <v>3.614208</v>
       </c>
       <c r="N53">
-        <v>19.44662933333334</v>
+        <v>19.37712533333334</v>
       </c>
       <c r="O53">
-        <v>4.861657333333334</v>
+        <v>4.844281333333334</v>
       </c>
       <c r="P53">
-        <v>14.584972</v>
+        <v>14.532844</v>
       </c>
       <c r="Q53">
-        <v>13.926972</v>
+        <v>13.874844</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2106212094953772</v>
+        <v>0.2135728787198646</v>
       </c>
       <c r="T53">
-        <v>1.008025999551385</v>
+        <v>1.026078041090629</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.486108101927083</v>
+        <v>6.361375253813099</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.123691981785535</v>
+        <v>0.1234098209183352</v>
       </c>
       <c r="C54">
-        <v>119.3275906933953</v>
+        <v>118.640517406472</v>
       </c>
       <c r="D54">
-        <v>163.0875906933953</v>
+        <v>163.6805174064719</v>
       </c>
       <c r="E54">
-        <v>-20.84</v>
+        <v>-19.56</v>
       </c>
       <c r="F54">
-        <v>66.56</v>
+        <v>67.84</v>
       </c>
       <c r="G54">
         <v>22.8</v>
@@ -5715,28 +5715,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M54">
-        <v>3.614208</v>
+        <v>3.683712</v>
       </c>
       <c r="N54">
-        <v>19.37712533333334</v>
+        <v>19.30762133333334</v>
       </c>
       <c r="O54">
-        <v>4.844281333333334</v>
+        <v>4.826905333333334</v>
       </c>
       <c r="P54">
-        <v>14.532844</v>
+        <v>14.480716</v>
       </c>
       <c r="Q54">
-        <v>13.874844</v>
+        <v>13.822716</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2135728787198646</v>
+        <v>0.2166501508900749</v>
       </c>
       <c r="T54">
-        <v>1.026078041090629</v>
+        <v>1.044898254610266</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.361375253813099</v>
+        <v>6.241349305627947</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1234098209183352</v>
+        <v>0.1231276600511354</v>
       </c>
       <c r="C55">
-        <v>118.640517406472</v>
+        <v>117.9577711796313</v>
       </c>
       <c r="D55">
-        <v>163.6805174064719</v>
+        <v>164.2777711796313</v>
       </c>
       <c r="E55">
-        <v>-19.56</v>
+        <v>-18.28</v>
       </c>
       <c r="F55">
-        <v>67.84</v>
+        <v>69.12</v>
       </c>
       <c r="G55">
         <v>22.8</v>
@@ -5797,28 +5797,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M55">
-        <v>3.683712</v>
+        <v>3.753216</v>
       </c>
       <c r="N55">
-        <v>19.30762133333334</v>
+        <v>19.23811733333334</v>
       </c>
       <c r="O55">
-        <v>4.826905333333334</v>
+        <v>4.809529333333334</v>
       </c>
       <c r="P55">
-        <v>14.480716</v>
+        <v>14.428588</v>
       </c>
       <c r="Q55">
-        <v>13.822716</v>
+        <v>13.770588</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2166501508900749</v>
+        <v>0.2198612175024682</v>
       </c>
       <c r="T55">
-        <v>1.044898254610266</v>
+        <v>1.064536738282931</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.241349305627947</v>
+        <v>6.125768762931132</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1231276600511354</v>
+        <v>0.1232579991839356</v>
       </c>
       <c r="C56">
-        <v>117.9577711796313</v>
+        <v>116.4013397915308</v>
       </c>
       <c r="D56">
-        <v>164.2777711796313</v>
+        <v>164.0013397915308</v>
       </c>
       <c r="E56">
-        <v>-18.28</v>
+        <v>-17</v>
       </c>
       <c r="F56">
-        <v>69.12</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G56">
         <v>22.8</v>
@@ -5879,45 +5879,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M56">
-        <v>3.753216</v>
+        <v>3.893120000000001</v>
       </c>
       <c r="N56">
-        <v>19.23811733333334</v>
+        <v>19.09821333333334</v>
       </c>
       <c r="O56">
-        <v>4.809529333333334</v>
+        <v>4.774553333333334</v>
       </c>
       <c r="P56">
-        <v>14.428588</v>
+        <v>14.32366</v>
       </c>
       <c r="Q56">
-        <v>13.770588</v>
+        <v>13.66566</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2198612175024682</v>
+        <v>0.2232149981865235</v>
       </c>
       <c r="T56">
-        <v>1.064536738282931</v>
+        <v>1.085048043452159</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.125768762931132</v>
+        <v>5.905631815441942</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1232579991839356</v>
+        <v>0.1229833383167357</v>
       </c>
       <c r="C57">
-        <v>116.4013397915308</v>
+        <v>115.7049469688237</v>
       </c>
       <c r="D57">
-        <v>164.0013397915308</v>
+        <v>164.5849469688237</v>
       </c>
       <c r="E57">
-        <v>-17</v>
+        <v>-15.72</v>
       </c>
       <c r="F57">
-        <v>70.40000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="G57">
         <v>22.8</v>
@@ -5961,28 +5961,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M57">
-        <v>3.893120000000001</v>
+        <v>3.963904</v>
       </c>
       <c r="N57">
-        <v>19.09821333333334</v>
+        <v>19.02742933333334</v>
       </c>
       <c r="O57">
-        <v>4.774553333333334</v>
+        <v>4.756857333333334</v>
       </c>
       <c r="P57">
-        <v>14.32366</v>
+        <v>14.270572</v>
       </c>
       <c r="Q57">
-        <v>13.66566</v>
+        <v>13.612572</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2232149981865235</v>
+        <v>0.2267212234471267</v>
       </c>
       <c r="T57">
-        <v>1.085048043452159</v>
+        <v>1.106491680674534</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.905631815441942</v>
+        <v>5.800174104451908</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1229833383167357</v>
+        <v>0.1227086774495359</v>
       </c>
       <c r="C58">
-        <v>115.7049469688237</v>
+        <v>115.0127225718063</v>
       </c>
       <c r="D58">
-        <v>164.5849469688237</v>
+        <v>165.1727225718063</v>
       </c>
       <c r="E58">
-        <v>-15.72</v>
+        <v>-14.44</v>
       </c>
       <c r="F58">
-        <v>71.68000000000001</v>
+        <v>72.96000000000001</v>
       </c>
       <c r="G58">
         <v>22.8</v>
@@ -6043,28 +6043,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M58">
-        <v>3.963904</v>
+        <v>4.034688000000001</v>
       </c>
       <c r="N58">
-        <v>19.02742933333334</v>
+        <v>18.95664533333333</v>
       </c>
       <c r="O58">
-        <v>4.756857333333334</v>
+        <v>4.739161333333334</v>
       </c>
       <c r="P58">
-        <v>14.270572</v>
+        <v>14.217484</v>
       </c>
       <c r="Q58">
-        <v>13.612572</v>
+        <v>13.559484</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2267212234471267</v>
+        <v>0.2303905289524092</v>
       </c>
       <c r="T58">
-        <v>1.106491680674534</v>
+        <v>1.128932696372368</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.800174104451908</v>
+        <v>5.698416664022925</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1227086774495359</v>
+        <v>0.1224340165823361</v>
       </c>
       <c r="C59">
-        <v>115.0127225718063</v>
+        <v>114.3247114201343</v>
       </c>
       <c r="D59">
-        <v>165.1727225718063</v>
+        <v>165.7647114201343</v>
       </c>
       <c r="E59">
-        <v>-14.44</v>
+        <v>-13.16</v>
       </c>
       <c r="F59">
-        <v>72.96000000000001</v>
+        <v>74.24000000000001</v>
       </c>
       <c r="G59">
         <v>22.8</v>
@@ -6125,28 +6125,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M59">
-        <v>4.034688000000001</v>
+        <v>4.105472000000001</v>
       </c>
       <c r="N59">
-        <v>18.95664533333333</v>
+        <v>18.88586133333334</v>
       </c>
       <c r="O59">
-        <v>4.739161333333334</v>
+        <v>4.721465333333335</v>
       </c>
       <c r="P59">
-        <v>14.217484</v>
+        <v>14.164396</v>
       </c>
       <c r="Q59">
-        <v>13.559484</v>
+        <v>13.506396</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2303905289524092</v>
+        <v>0.2342345632912765</v>
       </c>
       <c r="T59">
-        <v>1.128932696372368</v>
+        <v>1.152442331865337</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.698416664022925</v>
+        <v>5.600168100850118</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1224340165823361</v>
+        <v>0.1221593557151363</v>
       </c>
       <c r="C60">
-        <v>114.3247114201343</v>
+        <v>113.64095897832</v>
       </c>
       <c r="D60">
-        <v>165.7647114201343</v>
+        <v>166.36095897832</v>
       </c>
       <c r="E60">
-        <v>-13.16000000000001</v>
+        <v>-11.88000000000001</v>
       </c>
       <c r="F60">
-        <v>74.23999999999999</v>
+        <v>75.52</v>
       </c>
       <c r="G60">
         <v>22.8</v>
@@ -6207,28 +6207,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M60">
-        <v>4.105472</v>
+        <v>4.176256</v>
       </c>
       <c r="N60">
-        <v>18.88586133333334</v>
+        <v>18.81507733333334</v>
       </c>
       <c r="O60">
-        <v>4.721465333333335</v>
+        <v>4.703769333333335</v>
       </c>
       <c r="P60">
-        <v>14.164396</v>
+        <v>14.111308</v>
       </c>
       <c r="Q60">
-        <v>13.506396</v>
+        <v>13.45330800000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2342345632912765</v>
+        <v>0.2382661115003324</v>
       </c>
       <c r="T60">
-        <v>1.152442331865337</v>
+        <v>1.177098778845768</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.600168100850119</v>
+        <v>5.50524999744588</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1221593557151363</v>
+        <v>0.1218846948479365</v>
       </c>
       <c r="C61">
-        <v>113.64095897832</v>
+        <v>112.9615113673714</v>
       </c>
       <c r="D61">
-        <v>166.36095897832</v>
+        <v>166.9615113673714</v>
       </c>
       <c r="E61">
-        <v>-11.88000000000001</v>
+        <v>-10.60000000000001</v>
       </c>
       <c r="F61">
-        <v>75.52</v>
+        <v>76.8</v>
       </c>
       <c r="G61">
         <v>22.8</v>
@@ -6289,28 +6289,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M61">
-        <v>4.176256</v>
+        <v>4.24704</v>
       </c>
       <c r="N61">
-        <v>18.81507733333334</v>
+        <v>18.74429333333334</v>
       </c>
       <c r="O61">
-        <v>4.703769333333335</v>
+        <v>4.686073333333335</v>
       </c>
       <c r="P61">
-        <v>14.111308</v>
+        <v>14.05822</v>
       </c>
       <c r="Q61">
-        <v>13.45330800000001</v>
+        <v>13.40022</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2382661115003324</v>
+        <v>0.2424992371198413</v>
       </c>
       <c r="T61">
-        <v>1.177098778845768</v>
+        <v>1.20298804817522</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.50524999744588</v>
+        <v>5.413495830821781</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1218846948479365</v>
+        <v>0.1216100339807367</v>
       </c>
       <c r="C62">
-        <v>112.9615113673714</v>
+        <v>112.2864153766851</v>
       </c>
       <c r="D62">
-        <v>166.9615113673714</v>
+        <v>167.5664153766851</v>
       </c>
       <c r="E62">
-        <v>-10.60000000000001</v>
+        <v>-9.320000000000007</v>
       </c>
       <c r="F62">
-        <v>76.8</v>
+        <v>78.08</v>
       </c>
       <c r="G62">
         <v>22.8</v>
@@ -6371,28 +6371,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M62">
-        <v>4.24704</v>
+        <v>4.317824</v>
       </c>
       <c r="N62">
-        <v>18.74429333333334</v>
+        <v>18.67350933333334</v>
       </c>
       <c r="O62">
-        <v>4.686073333333335</v>
+        <v>4.668377333333334</v>
       </c>
       <c r="P62">
-        <v>14.05822</v>
+        <v>14.005132</v>
       </c>
       <c r="Q62">
-        <v>13.40022</v>
+        <v>13.347132</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2424992371198413</v>
+        <v>0.2469494461044531</v>
       </c>
       <c r="T62">
-        <v>1.20298804817522</v>
+        <v>1.23020497234208</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.413495830821781</v>
+        <v>5.32474999752962</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1216100339807367</v>
+        <v>0.1213353731135369</v>
       </c>
       <c r="C63">
-        <v>112.2864153766851</v>
+        <v>111.6157184761978</v>
       </c>
       <c r="D63">
-        <v>167.5664153766851</v>
+        <v>168.1757184761977</v>
       </c>
       <c r="E63">
-        <v>-9.320000000000007</v>
+        <v>-8.040000000000006</v>
       </c>
       <c r="F63">
-        <v>78.08</v>
+        <v>79.36</v>
       </c>
       <c r="G63">
         <v>22.8</v>
@@ -6453,28 +6453,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M63">
-        <v>4.317824</v>
+        <v>4.388608000000001</v>
       </c>
       <c r="N63">
-        <v>18.67350933333334</v>
+        <v>18.60272533333334</v>
       </c>
       <c r="O63">
-        <v>4.668377333333334</v>
+        <v>4.650681333333334</v>
       </c>
       <c r="P63">
-        <v>14.005132</v>
+        <v>13.952044</v>
       </c>
       <c r="Q63">
-        <v>13.347132</v>
+        <v>13.294044</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2469494461044531</v>
+        <v>0.2516338766145707</v>
       </c>
       <c r="T63">
-        <v>1.23020497234208</v>
+        <v>1.258854366201933</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.32474999752962</v>
+        <v>5.238866933053336</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1213353731135369</v>
+        <v>0.121060712246337</v>
       </c>
       <c r="C64">
-        <v>111.6157184761978</v>
+        <v>110.9494688288045</v>
       </c>
       <c r="D64">
-        <v>168.1757184761977</v>
+        <v>168.7894688288045</v>
       </c>
       <c r="E64">
-        <v>-8.040000000000006</v>
+        <v>-6.760000000000005</v>
       </c>
       <c r="F64">
-        <v>79.36</v>
+        <v>80.64</v>
       </c>
       <c r="G64">
         <v>22.8</v>
@@ -6535,28 +6535,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M64">
-        <v>4.388608000000001</v>
+        <v>4.459392</v>
       </c>
       <c r="N64">
-        <v>18.60272533333334</v>
+        <v>18.53194133333334</v>
       </c>
       <c r="O64">
-        <v>4.650681333333334</v>
+        <v>4.632985333333334</v>
       </c>
       <c r="P64">
-        <v>13.952044</v>
+        <v>13.898956</v>
       </c>
       <c r="Q64">
-        <v>13.294044</v>
+        <v>13.240956</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2516338766145707</v>
+        <v>0.2565715195846948</v>
       </c>
       <c r="T64">
-        <v>1.258854366201933</v>
+        <v>1.289052375946102</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.238866933053336</v>
+        <v>5.155710315068363</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.121060712246337</v>
+        <v>0.1207860513791372</v>
       </c>
       <c r="C65">
-        <v>110.9494688288045</v>
+        <v>110.2877153030497</v>
       </c>
       <c r="D65">
-        <v>168.7894688288045</v>
+        <v>169.4077153030497</v>
       </c>
       <c r="E65">
-        <v>-6.760000000000005</v>
+        <v>-5.480000000000004</v>
       </c>
       <c r="F65">
-        <v>80.64</v>
+        <v>81.92</v>
       </c>
       <c r="G65">
         <v>22.8</v>
@@ -6617,28 +6617,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M65">
-        <v>4.459392</v>
+        <v>4.530176</v>
       </c>
       <c r="N65">
-        <v>18.53194133333334</v>
+        <v>18.46115733333334</v>
       </c>
       <c r="O65">
-        <v>4.632985333333334</v>
+        <v>4.615289333333334</v>
       </c>
       <c r="P65">
-        <v>13.898956</v>
+        <v>13.845868</v>
       </c>
       <c r="Q65">
-        <v>13.240956</v>
+        <v>13.187868</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2565715195846948</v>
+        <v>0.261783476053159</v>
       </c>
       <c r="T65">
-        <v>1.289052375946102</v>
+        <v>1.320928052898281</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.155710315068363</v>
+        <v>5.07515234139542</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1207860513791372</v>
+        <v>0.1205113905119374</v>
       </c>
       <c r="C66">
-        <v>110.2877153030497</v>
+        <v>109.6305074860975</v>
       </c>
       <c r="D66">
-        <v>169.4077153030497</v>
+        <v>170.0305074860975</v>
       </c>
       <c r="E66">
-        <v>-5.480000000000004</v>
+        <v>-4.200000000000003</v>
       </c>
       <c r="F66">
-        <v>81.92</v>
+        <v>83.2</v>
       </c>
       <c r="G66">
         <v>22.8</v>
@@ -6699,28 +6699,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M66">
-        <v>4.530176</v>
+        <v>4.600960000000001</v>
       </c>
       <c r="N66">
-        <v>18.46115733333334</v>
+        <v>18.39037333333334</v>
       </c>
       <c r="O66">
-        <v>4.615289333333334</v>
+        <v>4.597593333333334</v>
       </c>
       <c r="P66">
-        <v>13.845868</v>
+        <v>13.79278</v>
       </c>
       <c r="Q66">
-        <v>13.187868</v>
+        <v>13.13478</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.261783476053159</v>
+        <v>0.2672932586055355</v>
       </c>
       <c r="T66">
-        <v>1.320928052898281</v>
+        <v>1.35462519710487</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.07515234139542</v>
+        <v>4.997073074604721</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1205113905119374</v>
+        <v>0.1202367296447376</v>
       </c>
       <c r="C67">
-        <v>109.6305074860975</v>
+        <v>108.9778956969908</v>
       </c>
       <c r="D67">
-        <v>170.0305074860975</v>
+        <v>170.6578956969908</v>
       </c>
       <c r="E67">
-        <v>-4.200000000000003</v>
+        <v>-2.920000000000002</v>
       </c>
       <c r="F67">
-        <v>83.2</v>
+        <v>84.48</v>
       </c>
       <c r="G67">
         <v>22.8</v>
@@ -6781,28 +6781,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M67">
-        <v>4.600960000000001</v>
+        <v>4.671744</v>
       </c>
       <c r="N67">
-        <v>18.39037333333334</v>
+        <v>18.31958933333334</v>
       </c>
       <c r="O67">
-        <v>4.597593333333334</v>
+        <v>4.579897333333334</v>
       </c>
       <c r="P67">
-        <v>13.79278</v>
+        <v>13.739692</v>
       </c>
       <c r="Q67">
-        <v>13.13478</v>
+        <v>13.081692</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2672932586055355</v>
+        <v>0.2731271460139342</v>
       </c>
       <c r="T67">
-        <v>1.35462519710487</v>
+        <v>1.390304526264787</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.997073074604721</v>
+        <v>4.921359846201619</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1202367296447376</v>
+        <v>0.1199620687775378</v>
       </c>
       <c r="C68">
-        <v>108.9778956969908</v>
+        <v>108.3299310002027</v>
       </c>
       <c r="D68">
-        <v>170.6578956969908</v>
+        <v>171.2899310002027</v>
       </c>
       <c r="E68">
-        <v>-2.920000000000002</v>
+        <v>-1.640000000000001</v>
       </c>
       <c r="F68">
-        <v>84.48</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="G68">
         <v>22.8</v>
@@ -6863,28 +6863,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M68">
-        <v>4.671744</v>
+        <v>4.742528</v>
       </c>
       <c r="N68">
-        <v>18.31958933333334</v>
+        <v>18.24880533333334</v>
       </c>
       <c r="O68">
-        <v>4.579897333333334</v>
+        <v>4.562201333333334</v>
       </c>
       <c r="P68">
-        <v>13.739692</v>
+        <v>13.686604</v>
       </c>
       <c r="Q68">
-        <v>13.081692</v>
+        <v>13.028604</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2731271460139342</v>
+        <v>0.2793146023561752</v>
       </c>
       <c r="T68">
-        <v>1.390304526264787</v>
+        <v>1.428146239010154</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.921359846201619</v>
+        <v>4.847906714168759</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1199620687775378</v>
+        <v>0.119687407910338</v>
       </c>
       <c r="C69">
-        <v>108.3299310002027</v>
+        <v>107.6866652194921</v>
       </c>
       <c r="D69">
-        <v>171.2899310002027</v>
+        <v>171.9266652194921</v>
       </c>
       <c r="E69">
-        <v>-1.640000000000001</v>
+        <v>-0.3599999999999994</v>
       </c>
       <c r="F69">
-        <v>85.76000000000001</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="G69">
         <v>22.8</v>
@@ -6945,28 +6945,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M69">
-        <v>4.742528</v>
+        <v>4.813312000000001</v>
       </c>
       <c r="N69">
-        <v>18.24880533333334</v>
+        <v>18.17802133333334</v>
       </c>
       <c r="O69">
-        <v>4.562201333333334</v>
+        <v>4.544505333333334</v>
       </c>
       <c r="P69">
-        <v>13.686604</v>
+        <v>13.633516</v>
       </c>
       <c r="Q69">
-        <v>13.028604</v>
+        <v>12.975516</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2793146023561752</v>
+        <v>0.2858887747198063</v>
       </c>
       <c r="T69">
-        <v>1.428146239010154</v>
+        <v>1.468353058802107</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.847906714168759</v>
+        <v>4.776613968372159</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.119687407910338</v>
+        <v>0.1194127470431382</v>
       </c>
       <c r="C70">
-        <v>107.6866652194921</v>
+        <v>107.0481509520689</v>
       </c>
       <c r="D70">
-        <v>171.9266652194921</v>
+        <v>172.5681509520689</v>
       </c>
       <c r="E70">
-        <v>-0.3599999999999994</v>
+        <v>0.9200000000000017</v>
       </c>
       <c r="F70">
-        <v>87.04000000000001</v>
+        <v>88.32000000000001</v>
       </c>
       <c r="G70">
         <v>22.8</v>
@@ -7027,28 +7027,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M70">
-        <v>4.813312000000001</v>
+        <v>4.884096</v>
       </c>
       <c r="N70">
-        <v>18.17802133333334</v>
+        <v>18.10723733333334</v>
       </c>
       <c r="O70">
-        <v>4.544505333333334</v>
+        <v>4.526809333333334</v>
       </c>
       <c r="P70">
-        <v>13.633516</v>
+        <v>13.580428</v>
       </c>
       <c r="Q70">
-        <v>12.975516</v>
+        <v>12.922428</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2858887747198063</v>
+        <v>0.2928870872359297</v>
       </c>
       <c r="T70">
-        <v>1.468353058802107</v>
+        <v>1.511153866967734</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.776613968372159</v>
+        <v>4.707387678975461</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1194127470431382</v>
+        <v>0.1191380861759384</v>
       </c>
       <c r="C71">
-        <v>107.0481509520689</v>
+        <v>106.4144415830769</v>
       </c>
       <c r="D71">
-        <v>172.5681509520689</v>
+        <v>173.2144415830769</v>
       </c>
       <c r="E71">
-        <v>0.9200000000000017</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="F71">
-        <v>88.32000000000001</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="G71">
         <v>22.8</v>
@@ -7109,28 +7109,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M71">
-        <v>4.884096</v>
+        <v>4.954880000000001</v>
       </c>
       <c r="N71">
-        <v>18.10723733333334</v>
+        <v>18.03645333333333</v>
       </c>
       <c r="O71">
-        <v>4.526809333333334</v>
+        <v>4.509113333333334</v>
       </c>
       <c r="P71">
-        <v>13.580428</v>
+        <v>13.52734</v>
       </c>
       <c r="Q71">
-        <v>12.922428</v>
+        <v>12.86934</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2928870872359297</v>
+        <v>0.3003519539197946</v>
       </c>
       <c r="T71">
-        <v>1.511153866967734</v>
+        <v>1.556808062344403</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.707387678975461</v>
+        <v>4.640139283561526</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1191380861759384</v>
+        <v>0.1188634253087386</v>
       </c>
       <c r="C72">
-        <v>106.4144415830769</v>
+        <v>105.7855913004041</v>
       </c>
       <c r="D72">
-        <v>173.2144415830769</v>
+        <v>173.865591300404</v>
       </c>
       <c r="E72">
-        <v>2.200000000000003</v>
+        <v>3.480000000000004</v>
       </c>
       <c r="F72">
-        <v>89.60000000000001</v>
+        <v>90.88000000000001</v>
       </c>
       <c r="G72">
         <v>22.8</v>
@@ -7191,28 +7191,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M72">
-        <v>4.954880000000001</v>
+        <v>5.025664000000001</v>
       </c>
       <c r="N72">
-        <v>18.03645333333333</v>
+        <v>17.96566933333334</v>
       </c>
       <c r="O72">
-        <v>4.509113333333334</v>
+        <v>4.491417333333334</v>
       </c>
       <c r="P72">
-        <v>13.52734</v>
+        <v>13.474252</v>
       </c>
       <c r="Q72">
-        <v>12.86934</v>
+        <v>12.816252</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3003519539197946</v>
+        <v>0.3083316389956503</v>
       </c>
       <c r="T72">
-        <v>1.556808062344403</v>
+        <v>1.605610822919463</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.640139283561526</v>
+        <v>4.574785209145167</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1188634253087386</v>
+        <v>0.1185887644415387</v>
       </c>
       <c r="C73">
-        <v>105.7855913004041</v>
+        <v>105.161655109828</v>
       </c>
       <c r="D73">
-        <v>173.865591300404</v>
+        <v>174.5216551098279</v>
       </c>
       <c r="E73">
-        <v>3.47999999999999</v>
+        <v>4.759999999999991</v>
       </c>
       <c r="F73">
-        <v>90.88</v>
+        <v>92.16</v>
       </c>
       <c r="G73">
         <v>22.8</v>
@@ -7273,28 +7273,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M73">
-        <v>5.025664</v>
+        <v>5.096448</v>
       </c>
       <c r="N73">
-        <v>17.96566933333334</v>
+        <v>17.89488533333334</v>
       </c>
       <c r="O73">
-        <v>4.491417333333334</v>
+        <v>4.473721333333335</v>
       </c>
       <c r="P73">
-        <v>13.474252</v>
+        <v>13.421164</v>
       </c>
       <c r="Q73">
-        <v>12.816252</v>
+        <v>12.76316400000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3083316389956502</v>
+        <v>0.3168813015769241</v>
       </c>
       <c r="T73">
-        <v>1.605610822919462</v>
+        <v>1.657899494964169</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.574785209145167</v>
+        <v>4.511246525684818</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1185887644415387</v>
+        <v>0.1196828535743389</v>
       </c>
       <c r="C74">
-        <v>105.161655109828</v>
+        <v>101.297263237337</v>
       </c>
       <c r="D74">
-        <v>174.5216551098279</v>
+        <v>171.937263237337</v>
       </c>
       <c r="E74">
-        <v>4.759999999999991</v>
+        <v>6.039999999999992</v>
       </c>
       <c r="F74">
-        <v>92.16</v>
+        <v>93.44</v>
       </c>
       <c r="G74">
         <v>22.8</v>
@@ -7355,45 +7355,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M74">
-        <v>5.096448</v>
+        <v>5.400832</v>
       </c>
       <c r="N74">
-        <v>17.89488533333334</v>
+        <v>17.59050133333334</v>
       </c>
       <c r="O74">
-        <v>4.473721333333335</v>
+        <v>4.397625333333334</v>
       </c>
       <c r="P74">
-        <v>13.421164</v>
+        <v>13.192876</v>
       </c>
       <c r="Q74">
-        <v>12.76316400000001</v>
+        <v>12.534876</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3168813015769241</v>
+        <v>0.3260642724975515</v>
       </c>
       <c r="T74">
-        <v>1.657899494964169</v>
+        <v>1.71406140197515</v>
       </c>
       <c r="U74">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.511246525684818</v>
+        <v>4.256998427896542</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1196828535743389</v>
+        <v>0.1194269427071391</v>
       </c>
       <c r="C75">
-        <v>101.297263237337</v>
+        <v>100.6148788997725</v>
       </c>
       <c r="D75">
-        <v>171.937263237337</v>
+        <v>172.5348788997725</v>
       </c>
       <c r="E75">
-        <v>6.039999999999992</v>
+        <v>7.319999999999993</v>
       </c>
       <c r="F75">
-        <v>93.44</v>
+        <v>94.72</v>
       </c>
       <c r="G75">
         <v>22.8</v>
@@ -7437,28 +7437,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M75">
-        <v>5.400832</v>
+        <v>5.474816000000001</v>
       </c>
       <c r="N75">
-        <v>17.59050133333334</v>
+        <v>17.51651733333334</v>
       </c>
       <c r="O75">
-        <v>4.397625333333334</v>
+        <v>4.379129333333334</v>
       </c>
       <c r="P75">
-        <v>13.192876</v>
+        <v>13.137388</v>
       </c>
       <c r="Q75">
-        <v>12.534876</v>
+        <v>12.479388</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3260642724975515</v>
+        <v>0.3359536257966889</v>
       </c>
       <c r="T75">
-        <v>1.71406140197515</v>
+        <v>1.774543455679284</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.256998427896542</v>
+        <v>4.199471422114156</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1194269427071391</v>
+        <v>0.1191710318399393</v>
       </c>
       <c r="C76">
-        <v>100.6148788997725</v>
+        <v>99.93666341028305</v>
       </c>
       <c r="D76">
-        <v>172.5348788997725</v>
+        <v>173.136663410283</v>
       </c>
       <c r="E76">
-        <v>7.319999999999993</v>
+        <v>8.599999999999994</v>
       </c>
       <c r="F76">
-        <v>94.72</v>
+        <v>96</v>
       </c>
       <c r="G76">
         <v>22.8</v>
@@ -7519,28 +7519,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M76">
-        <v>5.474816000000001</v>
+        <v>5.5488</v>
       </c>
       <c r="N76">
-        <v>17.51651733333334</v>
+        <v>17.44253333333334</v>
       </c>
       <c r="O76">
-        <v>4.379129333333334</v>
+        <v>4.360633333333334</v>
       </c>
       <c r="P76">
-        <v>13.137388</v>
+        <v>13.0819</v>
       </c>
       <c r="Q76">
-        <v>12.479388</v>
+        <v>12.4239</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3359536257966889</v>
+        <v>0.3466341273597572</v>
       </c>
       <c r="T76">
-        <v>1.774543455679284</v>
+        <v>1.839864073679748</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.199471422114156</v>
+        <v>4.143478469819301</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1191710318399393</v>
+        <v>0.1189151209727395</v>
       </c>
       <c r="C77">
-        <v>99.93666341028305</v>
+        <v>99.26266054313237</v>
       </c>
       <c r="D77">
-        <v>173.136663410283</v>
+        <v>173.7426605431324</v>
       </c>
       <c r="E77">
-        <v>8.599999999999994</v>
+        <v>9.879999999999995</v>
       </c>
       <c r="F77">
-        <v>96</v>
+        <v>97.28</v>
       </c>
       <c r="G77">
         <v>22.8</v>
@@ -7601,28 +7601,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M77">
-        <v>5.5488</v>
+        <v>5.622784</v>
       </c>
       <c r="N77">
-        <v>17.44253333333334</v>
+        <v>17.36854933333334</v>
       </c>
       <c r="O77">
-        <v>4.360633333333334</v>
+        <v>4.342137333333334</v>
       </c>
       <c r="P77">
-        <v>13.0819</v>
+        <v>13.026412</v>
       </c>
       <c r="Q77">
-        <v>12.4239</v>
+        <v>12.368412</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3466341273597572</v>
+        <v>0.3582046707197479</v>
       </c>
       <c r="T77">
-        <v>1.839864073679748</v>
+        <v>1.910628076513585</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.143478469819301</v>
+        <v>4.088959016269047</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1189151209727395</v>
+        <v>0.1186592101055397</v>
       </c>
       <c r="C78">
-        <v>99.26266054313237</v>
+        <v>98.59291468759523</v>
       </c>
       <c r="D78">
-        <v>173.7426605431324</v>
+        <v>174.3529146875952</v>
       </c>
       <c r="E78">
-        <v>9.879999999999995</v>
+        <v>11.16</v>
       </c>
       <c r="F78">
-        <v>97.28</v>
+        <v>98.56</v>
       </c>
       <c r="G78">
         <v>22.8</v>
@@ -7683,28 +7683,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M78">
-        <v>5.622784</v>
+        <v>5.696768</v>
       </c>
       <c r="N78">
-        <v>17.36854933333334</v>
+        <v>17.29456533333334</v>
       </c>
       <c r="O78">
-        <v>4.342137333333334</v>
+        <v>4.323641333333335</v>
       </c>
       <c r="P78">
-        <v>13.026412</v>
+        <v>12.970924</v>
       </c>
       <c r="Q78">
-        <v>12.368412</v>
+        <v>12.312924</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3582046707197479</v>
+        <v>0.3707813482849551</v>
       </c>
       <c r="T78">
-        <v>1.910628076513585</v>
+        <v>1.98754547089819</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.088959016269047</v>
+        <v>4.035855652421397</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1186592101055397</v>
+        <v>0.1204507992383399</v>
       </c>
       <c r="C79">
-        <v>98.59291468759523</v>
+        <v>93.12851491674985</v>
       </c>
       <c r="D79">
-        <v>174.3529146875952</v>
+        <v>170.1685149167498</v>
       </c>
       <c r="E79">
-        <v>11.16</v>
+        <v>12.44</v>
       </c>
       <c r="F79">
-        <v>98.56</v>
+        <v>99.84</v>
       </c>
       <c r="G79">
         <v>22.8</v>
@@ -7765,45 +7765,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M79">
-        <v>5.696768</v>
+        <v>6.120192</v>
       </c>
       <c r="N79">
-        <v>17.29456533333334</v>
+        <v>16.87114133333334</v>
       </c>
       <c r="O79">
-        <v>4.323641333333335</v>
+        <v>4.217785333333334</v>
       </c>
       <c r="P79">
-        <v>12.970924</v>
+        <v>12.653356</v>
       </c>
       <c r="Q79">
-        <v>12.312924</v>
+        <v>11.995356</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3707813482849551</v>
+        <v>0.3845013601742721</v>
       </c>
       <c r="T79">
-        <v>1.98754547089819</v>
+        <v>2.071455355681395</v>
       </c>
       <c r="U79">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>4.035855652421397</v>
+        <v>3.756635957390444</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1204507992383399</v>
+        <v>0.1202211383711401</v>
       </c>
       <c r="C80">
-        <v>93.12851491674985</v>
+        <v>92.37364862957998</v>
       </c>
       <c r="D80">
-        <v>170.1685149167498</v>
+        <v>170.69364862958</v>
       </c>
       <c r="E80">
-        <v>12.44</v>
+        <v>13.72</v>
       </c>
       <c r="F80">
-        <v>99.84</v>
+        <v>101.12</v>
       </c>
       <c r="G80">
         <v>22.8</v>
@@ -7847,28 +7847,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M80">
-        <v>6.120192</v>
+        <v>6.198656000000001</v>
       </c>
       <c r="N80">
-        <v>16.87114133333334</v>
+        <v>16.79267733333334</v>
       </c>
       <c r="O80">
-        <v>4.217785333333334</v>
+        <v>4.198169333333334</v>
       </c>
       <c r="P80">
-        <v>12.653356</v>
+        <v>12.594508</v>
       </c>
       <c r="Q80">
-        <v>11.995356</v>
+        <v>11.936508</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3845013601742721</v>
+        <v>0.3995280398625717</v>
       </c>
       <c r="T80">
-        <v>2.071455355681395</v>
+        <v>2.163356658063001</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.756635957390444</v>
+        <v>3.709083603499426</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1202211383711401</v>
+        <v>0.1199914775039402</v>
       </c>
       <c r="C81">
-        <v>92.37364862957998</v>
+        <v>91.62203346148593</v>
       </c>
       <c r="D81">
-        <v>170.69364862958</v>
+        <v>171.2220334614859</v>
       </c>
       <c r="E81">
-        <v>13.72</v>
+        <v>15</v>
       </c>
       <c r="F81">
-        <v>101.12</v>
+        <v>102.4</v>
       </c>
       <c r="G81">
         <v>22.8</v>
@@ -7929,28 +7929,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M81">
-        <v>6.198656000000001</v>
+        <v>6.27712</v>
       </c>
       <c r="N81">
-        <v>16.79267733333334</v>
+        <v>16.71421333333334</v>
       </c>
       <c r="O81">
-        <v>4.198169333333334</v>
+        <v>4.178553333333334</v>
       </c>
       <c r="P81">
-        <v>12.594508</v>
+        <v>12.53566</v>
       </c>
       <c r="Q81">
-        <v>11.936508</v>
+        <v>11.87766</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3995280398625717</v>
+        <v>0.4160573875197013</v>
       </c>
       <c r="T81">
-        <v>2.163356658063001</v>
+        <v>2.264448090682768</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.709083603499426</v>
+        <v>3.662720058455683</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1199914775039402</v>
+        <v>0.1197618166367404</v>
       </c>
       <c r="C82">
-        <v>91.62203346148593</v>
+        <v>90.87369969788477</v>
       </c>
       <c r="D82">
-        <v>171.2220334614859</v>
+        <v>171.7536996978848</v>
       </c>
       <c r="E82">
-        <v>15</v>
+        <v>16.28</v>
       </c>
       <c r="F82">
-        <v>102.4</v>
+        <v>103.68</v>
       </c>
       <c r="G82">
         <v>22.8</v>
@@ -8011,28 +8011,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M82">
-        <v>6.27712</v>
+        <v>6.355584</v>
       </c>
       <c r="N82">
-        <v>16.71421333333334</v>
+        <v>16.63574933333334</v>
       </c>
       <c r="O82">
-        <v>4.178553333333334</v>
+        <v>4.158937333333334</v>
       </c>
       <c r="P82">
-        <v>12.53566</v>
+        <v>12.476812</v>
       </c>
       <c r="Q82">
-        <v>11.87766</v>
+        <v>11.818812</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4160573875197013</v>
+        <v>0.4343266665091602</v>
       </c>
       <c r="T82">
-        <v>2.264448090682768</v>
+        <v>2.376180726736194</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.662720058455683</v>
+        <v>3.617501292301909</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1197618166367404</v>
+        <v>0.1195321557695406</v>
       </c>
       <c r="C83">
-        <v>90.87369969788477</v>
+        <v>90.12867800152594</v>
       </c>
       <c r="D83">
-        <v>171.7536996978848</v>
+        <v>172.2886780015259</v>
       </c>
       <c r="E83">
-        <v>16.28</v>
+        <v>17.56</v>
       </c>
       <c r="F83">
-        <v>103.68</v>
+        <v>104.96</v>
       </c>
       <c r="G83">
         <v>22.8</v>
@@ -8093,28 +8093,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M83">
-        <v>6.355584</v>
+        <v>6.434048000000001</v>
       </c>
       <c r="N83">
-        <v>16.63574933333334</v>
+        <v>16.55728533333334</v>
       </c>
       <c r="O83">
-        <v>4.158937333333334</v>
+        <v>4.139321333333334</v>
       </c>
       <c r="P83">
-        <v>12.476812</v>
+        <v>12.417964</v>
       </c>
       <c r="Q83">
-        <v>11.818812</v>
+        <v>11.759964</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4343266665091602</v>
+        <v>0.4546258653863369</v>
       </c>
       <c r="T83">
-        <v>2.376180726736194</v>
+        <v>2.50032810012889</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.617501292301909</v>
+        <v>3.573385422883593</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1195321557695406</v>
+        <v>0.1193024949023408</v>
       </c>
       <c r="C84">
-        <v>90.12867800152594</v>
+        <v>89.38699941838541</v>
       </c>
       <c r="D84">
-        <v>172.2886780015259</v>
+        <v>172.8269994183854</v>
       </c>
       <c r="E84">
-        <v>17.56</v>
+        <v>18.84</v>
       </c>
       <c r="F84">
-        <v>104.96</v>
+        <v>106.24</v>
       </c>
       <c r="G84">
         <v>22.8</v>
@@ -8175,28 +8175,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M84">
-        <v>6.434048000000001</v>
+        <v>6.512512000000001</v>
       </c>
       <c r="N84">
-        <v>16.55728533333334</v>
+        <v>16.47882133333334</v>
       </c>
       <c r="O84">
-        <v>4.139321333333334</v>
+        <v>4.119705333333334</v>
       </c>
       <c r="P84">
-        <v>12.417964</v>
+        <v>12.359116</v>
       </c>
       <c r="Q84">
-        <v>11.759964</v>
+        <v>11.701116</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4546258653863369</v>
+        <v>0.4773132053078872</v>
       </c>
       <c r="T84">
-        <v>2.50032810012889</v>
+        <v>2.639081046861903</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.573385422883593</v>
+        <v>3.530332586463309</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1193024949023408</v>
+        <v>0.120836834035141</v>
       </c>
       <c r="C85">
-        <v>89.38699941838541</v>
+        <v>84.57306529360778</v>
       </c>
       <c r="D85">
-        <v>172.8269994183854</v>
+        <v>169.2930652936078</v>
       </c>
       <c r="E85">
-        <v>18.84</v>
+        <v>20.12</v>
       </c>
       <c r="F85">
-        <v>106.24</v>
+        <v>107.52</v>
       </c>
       <c r="G85">
         <v>22.8</v>
@@ -8257,45 +8257,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M85">
-        <v>6.512512000000001</v>
+        <v>6.892032000000001</v>
       </c>
       <c r="N85">
-        <v>16.47882133333334</v>
+        <v>16.09930133333334</v>
       </c>
       <c r="O85">
-        <v>4.119705333333334</v>
+        <v>4.024825333333334</v>
       </c>
       <c r="P85">
-        <v>12.359116</v>
+        <v>12.074476</v>
       </c>
       <c r="Q85">
-        <v>11.701116</v>
+        <v>11.416476</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4773132053078872</v>
+        <v>0.5028364627196313</v>
       </c>
       <c r="T85">
-        <v>2.639081046861903</v>
+        <v>2.795178111936542</v>
       </c>
       <c r="U85">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.530332586463309</v>
+        <v>3.335929568135106</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.120836834035141</v>
+        <v>0.1206281731679412</v>
       </c>
       <c r="C86">
-        <v>84.5730652936078</v>
+        <v>83.7651446765402</v>
       </c>
       <c r="D86">
-        <v>169.2930652936078</v>
+        <v>169.7651446765402</v>
       </c>
       <c r="E86">
-        <v>20.11999999999999</v>
+        <v>21.39999999999999</v>
       </c>
       <c r="F86">
-        <v>107.52</v>
+        <v>108.8</v>
       </c>
       <c r="G86">
         <v>22.8</v>
@@ -8339,28 +8339,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M86">
-        <v>6.892032</v>
+        <v>6.97408</v>
       </c>
       <c r="N86">
-        <v>16.09930133333334</v>
+        <v>16.01725333333334</v>
       </c>
       <c r="O86">
-        <v>4.024825333333334</v>
+        <v>4.004313333333334</v>
       </c>
       <c r="P86">
-        <v>12.074476</v>
+        <v>12.01294</v>
       </c>
       <c r="Q86">
-        <v>11.416476</v>
+        <v>11.35494</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.502836462719631</v>
+        <v>0.5317628211196077</v>
       </c>
       <c r="T86">
-        <v>2.79517811193654</v>
+        <v>2.972088119021132</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.335929568135107</v>
+        <v>3.296683337921753</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1206281731679412</v>
+        <v>0.1204195123007414</v>
       </c>
       <c r="C87">
-        <v>83.7651446765402</v>
+        <v>82.95986424004708</v>
       </c>
       <c r="D87">
-        <v>169.7651446765402</v>
+        <v>170.2398642400471</v>
       </c>
       <c r="E87">
-        <v>21.39999999999999</v>
+        <v>22.67999999999999</v>
       </c>
       <c r="F87">
-        <v>108.8</v>
+        <v>110.08</v>
       </c>
       <c r="G87">
         <v>22.8</v>
@@ -8421,28 +8421,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M87">
-        <v>6.97408</v>
+        <v>7.056128</v>
       </c>
       <c r="N87">
-        <v>16.01725333333334</v>
+        <v>15.93520533333334</v>
       </c>
       <c r="O87">
-        <v>4.004313333333334</v>
+        <v>3.983801333333334</v>
       </c>
       <c r="P87">
-        <v>12.01294</v>
+        <v>11.951404</v>
       </c>
       <c r="Q87">
-        <v>11.35494</v>
+        <v>11.293404</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5317628211196077</v>
+        <v>0.5648215164338668</v>
       </c>
       <c r="T87">
-        <v>2.972088119021132</v>
+        <v>3.174270984260665</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.296683337921753</v>
+        <v>3.258349810736616</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1204195123007414</v>
+        <v>0.1202108514335415</v>
       </c>
       <c r="C88">
-        <v>82.95986424004708</v>
+        <v>82.15724619469434</v>
       </c>
       <c r="D88">
-        <v>170.2398642400471</v>
+        <v>170.7172461946943</v>
       </c>
       <c r="E88">
-        <v>22.67999999999999</v>
+        <v>23.95999999999999</v>
       </c>
       <c r="F88">
-        <v>110.08</v>
+        <v>111.36</v>
       </c>
       <c r="G88">
         <v>22.8</v>
@@ -8503,28 +8503,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M88">
-        <v>7.056128</v>
+        <v>7.138176000000001</v>
       </c>
       <c r="N88">
-        <v>15.93520533333334</v>
+        <v>15.85315733333334</v>
       </c>
       <c r="O88">
-        <v>3.983801333333334</v>
+        <v>3.963289333333334</v>
       </c>
       <c r="P88">
-        <v>11.951404</v>
+        <v>11.889868</v>
       </c>
       <c r="Q88">
-        <v>11.293404</v>
+        <v>11.231868</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5648215164338668</v>
+        <v>0.6029661648733964</v>
       </c>
       <c r="T88">
-        <v>3.174270984260665</v>
+        <v>3.407558905690895</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.258349810736616</v>
+        <v>3.220897514061482</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1202108514335415</v>
+        <v>0.1200021905663417</v>
       </c>
       <c r="C89">
-        <v>82.15724619469434</v>
+        <v>81.35731300087708</v>
       </c>
       <c r="D89">
-        <v>170.7172461946943</v>
+        <v>171.1973130008771</v>
       </c>
       <c r="E89">
-        <v>23.95999999999999</v>
+        <v>25.23999999999999</v>
       </c>
       <c r="F89">
-        <v>111.36</v>
+        <v>112.64</v>
       </c>
       <c r="G89">
         <v>22.8</v>
@@ -8585,28 +8585,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M89">
-        <v>7.138176000000001</v>
+        <v>7.220224000000001</v>
       </c>
       <c r="N89">
-        <v>15.85315733333334</v>
+        <v>15.77110933333334</v>
       </c>
       <c r="O89">
-        <v>3.963289333333334</v>
+        <v>3.942777333333334</v>
       </c>
       <c r="P89">
-        <v>11.889868</v>
+        <v>11.828332</v>
       </c>
       <c r="Q89">
-        <v>11.231868</v>
+        <v>11.170332</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6029661648733964</v>
+        <v>0.6474682547195144</v>
       </c>
       <c r="T89">
-        <v>3.407558905690895</v>
+        <v>3.679728147359497</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.220897514061482</v>
+        <v>3.184296405947147</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1200021905663417</v>
+        <v>0.1197935296991419</v>
       </c>
       <c r="C90">
-        <v>81.35731300087708</v>
+        <v>80.56008737234298</v>
       </c>
       <c r="D90">
-        <v>171.1973130008771</v>
+        <v>171.680087372343</v>
       </c>
       <c r="E90">
-        <v>25.23999999999999</v>
+        <v>26.52</v>
       </c>
       <c r="F90">
-        <v>112.64</v>
+        <v>113.92</v>
       </c>
       <c r="G90">
         <v>22.8</v>
@@ -8667,28 +8667,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M90">
-        <v>7.220224000000001</v>
+        <v>7.302272</v>
       </c>
       <c r="N90">
-        <v>15.77110933333334</v>
+        <v>15.68906133333334</v>
       </c>
       <c r="O90">
-        <v>3.942777333333334</v>
+        <v>3.922265333333334</v>
       </c>
       <c r="P90">
-        <v>11.828332</v>
+        <v>11.766796</v>
       </c>
       <c r="Q90">
-        <v>11.170332</v>
+        <v>11.108796</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6474682547195144</v>
+        <v>0.7000616336285628</v>
       </c>
       <c r="T90">
-        <v>3.679728147359497</v>
+        <v>4.001382705695117</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.184296405947147</v>
+        <v>3.14851779464437</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1197935296991419</v>
+        <v>0.1195848688319421</v>
       </c>
       <c r="C91">
-        <v>80.56008737234298</v>
+        <v>79.7655922797738</v>
       </c>
       <c r="D91">
-        <v>171.680087372343</v>
+        <v>172.1655922797738</v>
       </c>
       <c r="E91">
-        <v>26.52</v>
+        <v>27.8</v>
       </c>
       <c r="F91">
-        <v>113.92</v>
+        <v>115.2</v>
       </c>
       <c r="G91">
         <v>22.8</v>
@@ -8749,28 +8749,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M91">
-        <v>7.302272</v>
+        <v>7.384320000000001</v>
       </c>
       <c r="N91">
-        <v>15.68906133333334</v>
+        <v>15.60701333333334</v>
       </c>
       <c r="O91">
-        <v>3.922265333333334</v>
+        <v>3.901753333333334</v>
       </c>
       <c r="P91">
-        <v>11.766796</v>
+        <v>11.70526</v>
       </c>
       <c r="Q91">
-        <v>11.108796</v>
+        <v>11.04726</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7000616336285628</v>
+        <v>0.7631736883194212</v>
       </c>
       <c r="T91">
-        <v>4.001382705695117</v>
+        <v>4.387368175697863</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.14851779464437</v>
+        <v>3.113534263592766</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1195848688319421</v>
+        <v>0.1193762079647423</v>
       </c>
       <c r="C92">
-        <v>79.7655922797738</v>
+        <v>78.97385095442964</v>
       </c>
       <c r="D92">
-        <v>172.1655922797738</v>
+        <v>172.6538509544296</v>
       </c>
       <c r="E92">
-        <v>27.8</v>
+        <v>29.08</v>
       </c>
       <c r="F92">
-        <v>115.2</v>
+        <v>116.48</v>
       </c>
       <c r="G92">
         <v>22.8</v>
@@ -8831,28 +8831,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M92">
-        <v>7.384320000000001</v>
+        <v>7.466368000000001</v>
       </c>
       <c r="N92">
-        <v>15.60701333333334</v>
+        <v>15.52496533333334</v>
       </c>
       <c r="O92">
-        <v>3.901753333333334</v>
+        <v>3.881241333333334</v>
       </c>
       <c r="P92">
-        <v>11.70526</v>
+        <v>11.643724</v>
       </c>
       <c r="Q92">
-        <v>11.04726</v>
+        <v>10.985724</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7631736883194212</v>
+        <v>0.8403106440526923</v>
       </c>
       <c r="T92">
-        <v>4.387368175697863</v>
+        <v>4.859128194590106</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.113534263592766</v>
+        <v>3.079319601355483</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1193762079647423</v>
+        <v>0.1191675470975425</v>
       </c>
       <c r="C93">
-        <v>78.97385095442964</v>
+        <v>78.18488689185357</v>
       </c>
       <c r="D93">
-        <v>172.6538509544296</v>
+        <v>173.1448868918536</v>
       </c>
       <c r="E93">
-        <v>29.08</v>
+        <v>30.36</v>
       </c>
       <c r="F93">
-        <v>116.48</v>
+        <v>117.76</v>
       </c>
       <c r="G93">
         <v>22.8</v>
@@ -8913,28 +8913,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M93">
-        <v>7.466368000000001</v>
+        <v>7.548416</v>
       </c>
       <c r="N93">
-        <v>15.52496533333334</v>
+        <v>15.44291733333334</v>
       </c>
       <c r="O93">
-        <v>3.881241333333334</v>
+        <v>3.860729333333334</v>
       </c>
       <c r="P93">
-        <v>11.643724</v>
+        <v>11.582188</v>
       </c>
       <c r="Q93">
-        <v>10.985724</v>
+        <v>10.924188</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8403106440526923</v>
+        <v>0.9367318387192813</v>
       </c>
       <c r="T93">
-        <v>4.859128194590106</v>
+        <v>5.448828218205412</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.079319601355483</v>
+        <v>3.045848736123359</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1191675470975425</v>
+        <v>0.1189588862303427</v>
       </c>
       <c r="C94">
-        <v>78.18488689185357</v>
+        <v>77.39872385564108</v>
       </c>
       <c r="D94">
-        <v>173.1448868918536</v>
+        <v>173.6387238556411</v>
       </c>
       <c r="E94">
-        <v>30.36</v>
+        <v>31.64</v>
       </c>
       <c r="F94">
-        <v>117.76</v>
+        <v>119.04</v>
       </c>
       <c r="G94">
         <v>22.8</v>
@@ -8995,28 +8995,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M94">
-        <v>7.548416</v>
+        <v>7.630464000000001</v>
       </c>
       <c r="N94">
-        <v>15.44291733333334</v>
+        <v>15.36086933333334</v>
       </c>
       <c r="O94">
-        <v>3.860729333333334</v>
+        <v>3.840217333333334</v>
       </c>
       <c r="P94">
-        <v>11.582188</v>
+        <v>11.520652</v>
       </c>
       <c r="Q94">
-        <v>10.924188</v>
+        <v>10.862652</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9367318387192813</v>
+        <v>1.060701946147753</v>
       </c>
       <c r="T94">
-        <v>5.448828218205412</v>
+        <v>6.207013962853662</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.045848736123359</v>
+        <v>3.013097674444612</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1189588862303427</v>
+        <v>0.1242492253631428</v>
       </c>
       <c r="C95">
-        <v>77.39872385564108</v>
+        <v>64.40914059932813</v>
       </c>
       <c r="D95">
-        <v>173.6387238556411</v>
+        <v>161.9291405993281</v>
       </c>
       <c r="E95">
-        <v>31.64</v>
+        <v>32.92</v>
       </c>
       <c r="F95">
-        <v>119.04</v>
+        <v>120.32</v>
       </c>
       <c r="G95">
         <v>22.8</v>
@@ -9077,45 +9077,45 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M95">
-        <v>7.630464000000001</v>
+        <v>8.651008000000001</v>
       </c>
       <c r="N95">
-        <v>15.36086933333334</v>
+        <v>14.34032533333334</v>
       </c>
       <c r="O95">
-        <v>3.840217333333334</v>
+        <v>3.585081333333334</v>
       </c>
       <c r="P95">
-        <v>11.520652</v>
+        <v>10.755244</v>
       </c>
       <c r="Q95">
-        <v>10.862652</v>
+        <v>10.097244</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.060701946147753</v>
+        <v>1.225995422719049</v>
       </c>
       <c r="T95">
-        <v>6.207013962853662</v>
+        <v>7.217928289051327</v>
       </c>
       <c r="U95">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V95">
         <v>0.25</v>
       </c>
       <c r="W95">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y95">
-        <v>3.013097674444612</v>
+        <v>2.657647910316732</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1242492253631428</v>
+        <v>0.124099064495943</v>
       </c>
       <c r="C96">
-        <v>64.40914059932813</v>
+        <v>63.43968607434554</v>
       </c>
       <c r="D96">
-        <v>161.9291405993281</v>
+        <v>162.2396860743455</v>
       </c>
       <c r="E96">
-        <v>32.92</v>
+        <v>34.2</v>
       </c>
       <c r="F96">
-        <v>120.32</v>
+        <v>121.6</v>
       </c>
       <c r="G96">
         <v>22.8</v>
@@ -9159,28 +9159,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M96">
-        <v>8.651008000000001</v>
+        <v>8.743040000000001</v>
       </c>
       <c r="N96">
-        <v>14.34032533333334</v>
+        <v>14.24829333333334</v>
       </c>
       <c r="O96">
-        <v>3.585081333333334</v>
+        <v>3.562073333333334</v>
       </c>
       <c r="P96">
-        <v>10.755244</v>
+        <v>10.68622</v>
       </c>
       <c r="Q96">
-        <v>10.097244</v>
+        <v>10.02822</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.225995422719049</v>
+        <v>1.457406289918863</v>
       </c>
       <c r="T96">
-        <v>7.217928289051327</v>
+        <v>8.633208345728063</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.657647910316732</v>
+        <v>2.629672669155504</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.124099064495943</v>
+        <v>0.1239489036287432</v>
       </c>
       <c r="C97">
-        <v>63.43968607434554</v>
+        <v>62.47142495773265</v>
       </c>
       <c r="D97">
-        <v>162.2396860743455</v>
+        <v>162.5514249577326</v>
       </c>
       <c r="E97">
-        <v>34.2</v>
+        <v>35.48</v>
       </c>
       <c r="F97">
-        <v>121.6</v>
+        <v>122.88</v>
       </c>
       <c r="G97">
         <v>22.8</v>
@@ -9241,28 +9241,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M97">
-        <v>8.743040000000001</v>
+        <v>8.835072000000002</v>
       </c>
       <c r="N97">
-        <v>14.24829333333334</v>
+        <v>14.15626133333333</v>
       </c>
       <c r="O97">
-        <v>3.562073333333334</v>
+        <v>3.539065333333334</v>
       </c>
       <c r="P97">
-        <v>10.68622</v>
+        <v>10.617196</v>
       </c>
       <c r="Q97">
-        <v>10.02822</v>
+        <v>9.959196000000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.457406289918863</v>
+        <v>1.804522590718584</v>
       </c>
       <c r="T97">
-        <v>8.633208345728063</v>
+        <v>10.75612843074316</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.629672669155504</v>
+        <v>2.602280245518467</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1239489036287433</v>
+        <v>0.1237987427615434</v>
       </c>
       <c r="C98">
-        <v>62.47142495773258</v>
+        <v>61.50436414203259</v>
       </c>
       <c r="D98">
-        <v>162.5514249577326</v>
+        <v>162.8643641420326</v>
       </c>
       <c r="E98">
-        <v>35.47999999999999</v>
+        <v>36.75999999999999</v>
       </c>
       <c r="F98">
-        <v>122.88</v>
+        <v>124.16</v>
       </c>
       <c r="G98">
         <v>22.8</v>
@@ -9323,28 +9323,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M98">
-        <v>8.835072</v>
+        <v>8.927104</v>
       </c>
       <c r="N98">
-        <v>14.15626133333334</v>
+        <v>14.06422933333334</v>
       </c>
       <c r="O98">
-        <v>3.539065333333334</v>
+        <v>3.516057333333334</v>
       </c>
       <c r="P98">
-        <v>10.617196</v>
+        <v>10.548172</v>
       </c>
       <c r="Q98">
-        <v>9.959196000000004</v>
+        <v>9.890172000000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.80452259071858</v>
+        <v>2.383049758718112</v>
       </c>
       <c r="T98">
-        <v>10.75612843074314</v>
+        <v>14.29432857243496</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.602280245518467</v>
+        <v>2.57545261412137</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1237987427615434</v>
+        <v>0.1236485818943436</v>
       </c>
       <c r="C99">
-        <v>61.50436414203259</v>
+        <v>60.53851057296825</v>
       </c>
       <c r="D99">
-        <v>162.8643641420326</v>
+        <v>163.1785105729682</v>
       </c>
       <c r="E99">
-        <v>36.75999999999999</v>
+        <v>38.03999999999999</v>
       </c>
       <c r="F99">
-        <v>124.16</v>
+        <v>125.44</v>
       </c>
       <c r="G99">
         <v>22.8</v>
@@ -9405,28 +9405,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M99">
-        <v>8.927104</v>
+        <v>9.019136000000001</v>
       </c>
       <c r="N99">
-        <v>14.06422933333334</v>
+        <v>13.97219733333334</v>
       </c>
       <c r="O99">
-        <v>3.516057333333334</v>
+        <v>3.493049333333334</v>
       </c>
       <c r="P99">
-        <v>10.548172</v>
+        <v>10.479148</v>
       </c>
       <c r="Q99">
-        <v>9.890172000000003</v>
+        <v>9.821148000000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.383049758718112</v>
+        <v>3.540104094717177</v>
       </c>
       <c r="T99">
-        <v>14.29432857243496</v>
+        <v>21.3707288558186</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.57545261412137</v>
+        <v>2.549172485405845</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1236485818943436</v>
+        <v>0.1234984210271438</v>
       </c>
       <c r="C100">
-        <v>60.53851057296825</v>
+        <v>59.5738712499562</v>
       </c>
       <c r="D100">
-        <v>163.1785105729682</v>
+        <v>163.4938712499562</v>
       </c>
       <c r="E100">
-        <v>38.03999999999999</v>
+        <v>39.31999999999999</v>
       </c>
       <c r="F100">
-        <v>125.44</v>
+        <v>126.72</v>
       </c>
       <c r="G100">
         <v>22.8</v>
@@ -9487,28 +9487,28 @@
         <v>22.99133333333334</v>
       </c>
       <c r="M100">
-        <v>9.019136000000001</v>
+        <v>9.111168000000001</v>
       </c>
       <c r="N100">
-        <v>13.97219733333334</v>
+        <v>13.88016533333334</v>
       </c>
       <c r="O100">
-        <v>3.493049333333334</v>
+        <v>3.470041333333334</v>
       </c>
       <c r="P100">
-        <v>10.479148</v>
+        <v>10.410124</v>
       </c>
       <c r="Q100">
-        <v>9.821148000000003</v>
+        <v>9.752124000000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.540104094717177</v>
+        <v>7.011267102714373</v>
       </c>
       <c r="T100">
-        <v>21.3707288558186</v>
+        <v>42.59992970596953</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.549172485405845</v>
+        <v>2.523423268381544</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1234984210271438</v>
-      </c>
-      <c r="C101">
-        <v>59.5738712499562</v>
-      </c>
-      <c r="D101">
-        <v>163.4938712499562</v>
-      </c>
-      <c r="E101">
-        <v>39.31999999999999</v>
-      </c>
-      <c r="F101">
-        <v>126.72</v>
-      </c>
-      <c r="G101">
-        <v>22.8</v>
-      </c>
-      <c r="H101">
-        <v>40.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.33333333333334</v>
-      </c>
-      <c r="K101">
-        <v>-0.658</v>
-      </c>
-      <c r="L101">
-        <v>22.99133333333334</v>
-      </c>
-      <c r="M101">
-        <v>9.111168000000001</v>
-      </c>
-      <c r="N101">
-        <v>13.88016533333334</v>
-      </c>
-      <c r="O101">
-        <v>3.470041333333334</v>
-      </c>
-      <c r="P101">
-        <v>10.410124</v>
-      </c>
-      <c r="Q101">
-        <v>9.752124000000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.011267102714373</v>
-      </c>
-      <c r="T101">
-        <v>42.59992970596953</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.053925</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.523423268381544</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
